--- a/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
+++ b/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
@@ -19,14 +19,16 @@
     <sheet name="EC - Ecuador" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="GT - Guatemala" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="HN - Honduras" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MX - México" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="PA - Panamá" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="PE - Perú" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="PY - Paraguay" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="TT - Trinidad y Tobago" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="UY - Uruguay" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="VE - Venezuela" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="LATAM - Regional" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="JM - Jamaica" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="MX - México" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="PA - Panamá" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="PE - Perú" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="PY - Paraguay" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SV - El Salvador" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="TT - Trinidad y Tobago" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="UY - Uruguay" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="VE - Venezuela" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="LATAM - Regional" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AR - Argentina'!$A$1:$F$6</definedName>
@@ -40,14 +42,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'EC - Ecuador'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'GT - Guatemala'!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'HN - Honduras'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'MX - México'!$A$1:$F$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'PA - Panamá'!$A$1:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'PE - Perú'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'PY - Paraguay'!$A$1:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'TT - Trinidad y Tobago'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'UY - Uruguay'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'VE - Venezuela'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'LATAM - Regional'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'JM - Jamaica'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'MX - México'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'PA - Panamá'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'PE - Perú'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'PY - Paraguay'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'SV - El Salvador'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'TT - Trinidad y Tobago'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'UY - Uruguay'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'VE - Venezuela'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'LATAM - Regional'!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -607,139 +611,131 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ÍNDICE</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>País — casos (de los cuales SÍ / DUDA / NO)</t>
+          <t>Los 20 países del ILIA tienen pestaña. Los que no tienen casos identificados este ciclo se marcan «SIN CASOS» (por favor confirme si conoce alguno).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>AR — Argentina</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>5 casos  (SÍ 0 · DUDA 0 · NO 5)</t>
-        </is>
-      </c>
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>BO — Bolivia</t>
+          <t>ÍNDICE (20 países ILIA + Regional)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1 casos  (SÍ 1 · DUDA 0 · NO 0)</t>
+          <t>País — casos (de los cuales SÍ / DUDA / NO)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>BR — Brasil</t>
+          <t>AR — Argentina</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>23 casos  (SÍ 9 · DUDA 0 · NO 14)</t>
+          <t>5 casos  (SÍ 0 · DUDA 0 · NO 5)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>CL — Chile</t>
+          <t>BO — Bolivia</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>17 casos  (SÍ 10 · DUDA 2 · NO 5)</t>
+          <t>1 casos  (SÍ 1 · DUDA 0 · NO 0)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>CO — Colombia</t>
+          <t>BR — Brasil</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19 casos  (SÍ 4 · DUDA 1 · NO 14)</t>
+          <t>23 casos  (SÍ 9 · DUDA 0 · NO 14)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>CR — Costa Rica</t>
+          <t>CL — Chile</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 casos  (SÍ 0 · DUDA 0 · NO 2)</t>
+          <t>17 casos  (SÍ 10 · DUDA 2 · NO 5)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CU — Cuba</t>
+          <t>CO — Colombia</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1 casos  (SÍ 0 · DUDA 0 · NO 1)</t>
+          <t>19 casos  (SÍ 4 · DUDA 1 · NO 14)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DO — Rep. Dominicana</t>
+          <t>CR — Costa Rica</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>3 casos  (SÍ 0 · DUDA 0 · NO 3)</t>
+          <t>2 casos  (SÍ 0 · DUDA 0 · NO 2)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>EC — Ecuador</t>
+          <t>CU — Cuba</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1 casos  (SÍ 1 · DUDA 0 · NO 0)</t>
+          <t>1 casos  (SÍ 0 · DUDA 0 · NO 1)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GT — Guatemala</t>
+          <t>DO — Rep. Dominicana</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2 casos  (SÍ 1 · DUDA 0 · NO 1)</t>
+          <t>3 casos  (SÍ 0 · DUDA 0 · NO 3)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>HN — Honduras</t>
+          <t>EC — Ecuador</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -751,96 +747,160 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MX — México</t>
+          <t>GT — Guatemala</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>14 casos  (SÍ 2 · DUDA 1 · NO 11)</t>
+          <t>2 casos  (SÍ 1 · DUDA 0 · NO 1)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>PA — Panamá</t>
+          <t>HN — Honduras</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2 casos  (SÍ 1 · DUDA 0 · NO 1)</t>
+          <t>1 casos  (SÍ 1 · DUDA 0 · NO 0)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>PE — Perú</t>
+          <t>JM — Jamaica</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>3 casos  (SÍ 1 · DUDA 0 · NO 2)</t>
+          <t>SIN CASOS identificados este ciclo</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PY — Paraguay</t>
+          <t>MX — México</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2 casos  (SÍ 0 · DUDA 0 · NO 2)</t>
+          <t>14 casos  (SÍ 2 · DUDA 1 · NO 11)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>TT — Trinidad y Tobago</t>
+          <t>PA — Panamá</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1 casos  (SÍ 1 · DUDA 0 · NO 0)</t>
+          <t>2 casos  (SÍ 1 · DUDA 0 · NO 1)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>UY — Uruguay</t>
+          <t>PE — Perú</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>4 casos  (SÍ 1 · DUDA 0 · NO 3)</t>
+          <t>3 casos  (SÍ 1 · DUDA 0 · NO 2)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>VE — Venezuela</t>
+          <t>PY — Paraguay</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1 casos  (SÍ 0 · DUDA 0 · NO 1)</t>
+          <t>2 casos  (SÍ 0 · DUDA 0 · NO 2)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>SV — El Salvador</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SIN CASOS identificados este ciclo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>TT — Trinidad y Tobago</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1 casos  (SÍ 1 · DUDA 0 · NO 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>UY — Uruguay</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>4 casos  (SÍ 1 · DUDA 0 · NO 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>VE — Venezuela</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1 casos  (SÍ 0 · DUDA 0 · NO 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>LATAM — LATAM / Regional</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>5 casos  (SÍ 0 · DUDA 0 · NO 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Países SIN casos</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>JM (Jamaica), SV (El Salvador)</t>
         </is>
       </c>
     </row>
@@ -1120,6 +1180,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Caso</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Descripción breve</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Fuente (URL validada)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>¿Se incluye?</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Motivo (si NO/DUDA)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comentario / corrección (partner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>(sin casos identificados este ciclo)</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>No se identificaron casos de IA en participación ciudadana para este país. Si conoce alguno, agréguelo en las filas de abajo.</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1553,7 +1688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1660,7 +1795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1795,7 +1930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1906,7 +2041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1958,22 +2093,18 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+          <t>(sin casos identificados este ciclo)</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MP…</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>https://support.govocal.com/en/articles/8316692-ai-analysis</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>SÍ</t>
+          <t>No se identificaron casos de IA en participación ciudadana para este país. Si conoce alguno, agréguelo en las filas de abajo.</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
@@ -1981,169 +2112,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Caso</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Descripción breve</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Fuente (URL validada)</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>¿Se incluye?</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Motivo (si NO/DUDA)</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Comentario / corrección (partner)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC).</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Chatbot (Asistente virtual entrenado con IA)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Asistente Virtual de AGESIC – Chatbot gubernamental piloto lanzado en 2018 para adquirir experiencia en soluciones de IA en la atención ciudadana.</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Atencion ciudadana</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Es una iniciativa del gobierno uruguayo para definir una política pública de IA que abarque los sectores público, privado, académico y de la sociedad civil.</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>No evidencia de uso de IA</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Consulta pública nacional y participación multiactores impulsada por el Parlamento de Uruguay junto a Agesic, el Consejo Nacional Consultivo Honorario de los Derechos de la Niñez y la Adolescencia, Ceibal, UNICEF y PNUD.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2200,29 +2168,25 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Proceso de consulta/debate para la elaboración del Plan de la Patria de las 7 Grandes Transformaciones (7T) 2025-2031, conducido por el Gobierno Bolivariano de Venezuela (Ministerio del Poder Popular de Planificación / Vicepres…</t>
+          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MP…</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 prop</t>
-        </is>
-      </c>
+          <t>https://support.govocal.com/en/articles/8316692-ai-analysis</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2432,6 +2396,252 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Caso</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Descripción breve</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Fuente (URL validada)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>¿Se incluye?</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Motivo (si NO/DUDA)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comentario / corrección (partner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC).</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Asistente Virtual de AGESIC – Chatbot gubernamental piloto lanzado en 2018 para adquirir experiencia en soluciones de IA en la atención ciudadana.</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Atencion ciudadana</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Es una iniciativa del gobierno uruguayo para definir una política pública de IA que abarque los sectores público, privado, académico y de la sociedad civil.</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>No evidencia de uso de IA</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Consulta pública nacional y participación multiactores impulsada por el Parlamento de Uruguay junto a Agesic, el Consejo Nacional Consultivo Honorario de los Derechos de la Niñez y la Adolescencia, Ceibal, UNICEF y PNUD.</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Caso</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Descripción breve</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Fuente (URL validada)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>¿Se incluye?</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Motivo (si NO/DUDA)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comentario / corrección (partner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Proceso de consulta/debate para la elaboración del Plan de la Patria de las 7 Grandes Transformaciones (7T) 2025-2031, conducido por el Gobierno Bolivariano de Venezuela (Ministerio del Poder Popular de Planificación / Vicepres…</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 prop</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
+++ b/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
@@ -971,7 +971,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>https://www.gobiernoabierto.ec/boletin-014-2023/</t>
+          <t>https://ia.gobiernoabierto.ec/</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=para%20identificar%20posibles%20trastornos,de%20las%20dificultades%20de%20%C3%ADndole</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://osf.io/cu6w3</t>
+          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=virtual%2Fchatbot%20que%20funciona%20por%20WhatsApp,que%20realice%20una%20observaci%C3%B3n%20f%C3%ADsica</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>https://www.latinno.net/en/case/17232/</t>
+          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/paraempleo</t>
+          <t>https://fairlac.iadb.org/en/paraempleo</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.01545</t>
+          <t>https://arxiv.org/abs/2509.21292</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=Jaque%20y%20la%20Gu%C3%ADa%20de,Contiene%20informaci%C3%B3n%2C%20entre</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/estudio-dialogos-percepciones-de-futuro</t>
+          <t>https://estudiodialogos.cl/</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+          <t>https://ipp.unab.cl/</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.15532?utm_source=chatgpt.com</t>
+          <t>https://arxiv.org/abs/2303.15532</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://www.govocal.com/</t>
+          <t>https://vinadecide.cl/pages/presupuestoparticipativo</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf?utm_source=chatgpt.com</t>
+          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/latin-america/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica-0</t>
+          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">

--- a/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
+++ b/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
@@ -28,7 +28,6 @@
     <sheet name="TT - Trinidad y Tobago" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="UY - Uruguay" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="VE - Venezuela" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="LATAM - Regional" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AR - Argentina'!$A$1:$F$6</definedName>
@@ -51,7 +50,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'TT - Trinidad y Tobago'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'UY - Uruguay'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'VE - Venezuela'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'LATAM - Regional'!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -525,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -680,7 +678,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>17 casos  (SÍ 10 · DUDA 2 · NO 5)</t>
+          <t>17 casos  (SÍ 10 · DUDA 0 · NO 7)</t>
         </is>
       </c>
     </row>
@@ -692,7 +690,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>19 casos  (SÍ 4 · DUDA 1 · NO 14)</t>
+          <t>19 casos  (SÍ 5 · DUDA 0 · NO 14)</t>
         </is>
       </c>
     </row>
@@ -788,7 +786,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14 casos  (SÍ 2 · DUDA 1 · NO 11)</t>
+          <t>14 casos  (SÍ 2 · DUDA 0 · NO 12)</t>
         </is>
       </c>
     </row>
@@ -877,28 +875,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>LATAM — LATAM / Regional</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>5 casos  (SÍ 0 · DUDA 0 · NO 5)</t>
-        </is>
-      </c>
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Países SIN casos</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>JM (Jamaica), SV (El Salvador)</t>
         </is>
@@ -919,11 +905,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -966,7 +952,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -998,11 +984,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1045,7 +1031,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarroll…</t>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -1069,7 +1055,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>No hay un proceso participativo ciudadano cuyos aportes sean tratados por la IA.</t>
+          <t>No hay un proceso participativo ciudadano cuyos aportes sean tratados por la IA. La 'Plataforma IA de SEGEPLAN' (con modelos generativos / agentes) fue lanzada por SEGEPLAN con acompanamiento de Red Ciudadana (sociedad civil) y, en la linea conexa 'IA inclusiva para el desarrollo municipal', del PNUD (Programa Conjunto de Transformacion Digital, Joint sdg Fund / UE). Es una herramienta interna de productividad y un proceso de fortalecimiento de capacidades (curso de IA a 70+ personas del equipo tecnico central y territorial + 'Comunidad de practica de IA'). SEGEPLAN es el ente rector de los Planes de Desarrollo Municipal (PDM), que si se construyen con aportes participativos de los Consejos de Desarrollo (COCODES/COMUDES), pero no se halla evidencia de que la plataforma de IA sistematice/clasifique/resuma el contenido de esos aportes participativos.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1084,7 +1070,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en l</t>
+          <t>El criterio elegible exige que la IA generativa se use para sistematizar/clasificar/resumir el contenido de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=14176 del 04-nov-2025; nota ?p=14622 comunidad de practica feb-2026; blog Red Ciudadana; blog PNUD/unsdg 'IA inclusiva para el desarrollo municipal') describe la plataforma como (a) herramienta interna de productividad con 'agentes' para 'tareas repetitivas', (b) analisis de datos/documentos institucionales para estadisticas y alertas sobre la 'papeleria', y (c) un proceso de fortalecimiento de capacidades / comunidad de practica del equipo tecnico. Coincide exactamente con la exclusion del criterio ('solo herramienta interna de productividad/capacitacion del equipo tecnico o comunidad de practica sin aplicarse a los aportes'). Aunque SEGEPLAN es el ente rector de los PDM (que si integran aportes de COCODES/COMUDES) y la linea del PNUD prototipa soluciones municipales (atencion ciudadana, catastro, ordenamiento territorial), no se halla ninguna cita que conecte la IA con el tratamiento del contenido de los aportes participativos. Se decide entra=NOapoyo',no'). Confirma la tendencia previa , resuelta a no con evidencia multiple.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
@@ -1105,11 +1091,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1152,7 +1138,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias.</t>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -1165,7 +1151,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
+        </is>
+      </c>
       <c r="F2" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1184,11 +1174,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1259,11 +1249,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1306,7 +1296,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales …</t>
+          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (copladeg), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e iplaneg. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -1330,7 +1320,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
+          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1343,7 +1333,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Presupuesto participativo (Hermosillo); la IA (chatbot) facilita la votación (Implementación).</t>
+        </is>
+      </c>
       <c r="F3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1354,7 +1348,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>AMIMgo, un chatbot de atención ciudadana disponible a través de WhatsApp.</t>
+          <t>AMIMgo, un chatbot de atención ciudadana disponible a través de WhatsApp. Esta herramienta permite a los usuarios reportar y dar seguimiento a incidencias relacionadas con semáforos, señalización vial, infraestructura ciclista y el sistema de bicicletas públicas MiBici.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1369,7 +1363,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
@@ -1382,7 +1376,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ATIC es un chatbot que funciona a través de WhatsApp, así como por medio de una computadora y está entrenado para comprender una amplia gama de preguntas relacionadas al derecho de acceso a la información; obtener detalles sobr…</t>
+          <t>Atic es un chatbot que funciona a través de WhatsApp, así como por medio de una computadora y está entrenado para comprender una amplia gama de preguntas relacionadas al derecho de acceso a la información; obtener detalles sobre el presupuesto público, salarios de los funcionarios, facturas y empresas que intervienen en proyectos dentro de la Ciudad de México.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1397,7 +1391,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
@@ -1410,7 +1404,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Chatbot generativo que combina GPT-4 con recuperación aumentada de información sobre más de 1000 discursos, artículos y debates de Claudia Sheinbaum.</t>
+          <t>Chatbot generativo que combina gpt-4 con recuperación aumentada de información sobre más de 1000 discursos, artículos y debates de Claudia Sheinbaum. Responde preguntas del público emulando su tono y razonamiento técnico para dialogar sobre transición energética, cambio climático y política pública, fomentando un debate ciudadano informado.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1425,7 +1419,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>No es participación</t>
+          <t>No es participación.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
@@ -1453,7 +1447,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>No es participación, es informativo</t>
+          <t>No es participación, es informativo.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
@@ -1466,7 +1460,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Chatbot desarrollado por Cívica Digital e implementado en San Pedro Garza García en febrero de 2020, un mes antes del inicio de la pandemia, como única vía de comunicación entre la ciudadanía y el gobierno municipal a través de…</t>
+          <t>Chatbot desarrollado por Cívica Digital e implementado en San Pedro Garza García en febrero de 2020, un mes antes del inicio de la pandemia, como única vía de comunicación entre la ciudadanía y el gobierno municipal a través de WhatsApp y Facebook Chat. Inicialmente concebido para reportes de servicios públicos (luminarias, baches, recolección de basura, etc.).</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1481,7 +1475,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -1494,7 +1488,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Chatbot para ayudar a los ciudadanos a mantenerse informados y seguros durante la pandemia por Covid-19.</t>
+          <t>Chatbot para ayudar a los ciudadanos a mantenerse informados y seguros durante la pandemia por Covid-19. Este servicio, disponible en redes sociales desde el 2019 para brindar información general sobre la ciudad, ahora en su versión para WhatsApp incorporó información oficial y confiable sobre la enfermedad y su propagación; datos sobre la capacidad hospitalaria en la ciudad; y una asesoría rápida las 24 horas del día para determinar si un caso requería de atención médica.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1509,7 +1503,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
@@ -1522,7 +1516,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Algoritmos que analizan grandes volúmenes de texto en redes sociales para detectar indicios de depresión, anorexia u otros trastornos mentales en la población, con el fin de fundamentar políticas públicas de salud y asistir a q…</t>
+          <t>Algoritmos que analizan grandes volúmenes de texto en redes sociales para detectar indicios de depresión, anorexia u otros trastornos mentales en la población, con el fin de fundamentar políticas públicas de salud y asistir a quienes lo necesiten​oecd.org​oecd.org.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1537,7 +1531,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -1550,7 +1544,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Consulta ciudadana '¡Armemos un Plan!' convocada por el Gobierno de Jalisco a través de la Secretaría de Planeación y Participación Ciudadana (SPPC) para construir el Plan Estatal de Desarrollo y Gobernanza 2024-2030.</t>
+          <t>Consulta ciudadana '¡Armemos un Plan!' convocada por el Gobierno de Jalisco a través de la Secretaría de Planeación y Participación Ciudadana (sppc) para construir el Plan Estatal de Desarrollo y Gobernanza 2024-2030. Ejercicio abierto e inclusivo del 20 de febrero al 17 de abril de 2025 que registró 675,484 participaciones (aprox. 624,226 participaciones digitales + 25,176 niñas, niños y adolescentes mediante un mecanismo especialmente diseñado). Combinó: una encuesta representativa 'casa por casa' con rigor estadístico y metodológico; consulta digital abierta que recibió 15,899 propuestas ciudadanas escritas (temas: espacios públicos/deportivos/recreativos, medio ambiente y movilidad, agua y territorio, turismo rural, vivienda digna, economías locales); 12 foros regionales y 9 foros temáticos / mesas de trabajo con 5,563 participantes presenciales; 168 mesas regionales y 47 sectoriales donde se identificaron y discutieron 1,349 problemáticas; e instalación de 18 Consejos de Participación y Planeación (1 estatal, 12 regionales, 5 sectoriales). El resultado se estructuró en 5 ejes, 36 temas, 50 objetivos estratégicos, 197-198 proyectos y 82 indicadores de seguimiento.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1558,14 +1552,14 @@
           <t>https://armemosunplan.mx/propuestas-ciudadanas/</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>DUDA</t>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Pendiente de validación: confirmar si hay IA en el proceso.</t>
+          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero no hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas. Sin uso de IA.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -1578,7 +1572,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>El Chatbot MOVIMEX es una herramienta digital implementada por la Secretaría de Movilidad del Estado de México (Semov) en colaboración con Meta, que permite a los ciudadanos realizar trámites y presentar denuncias relacionadas …</t>
+          <t>El Chatbot movimex es una herramienta digital implementada por la Secretaría de Movilidad del Estado de México (Semov) en colaboración con Meta, que permite a los ciudadanos realizar trámites y presentar denuncias relacionadas con la movilidad a través de WhatsApp.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1593,7 +1587,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -1621,7 +1615,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -1649,7 +1643,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
+          <t>Integridad/proceso electoral, no contenido.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -1662,7 +1656,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Plataforma digital que mediante un chatbot con inteligencia artificial, ofrece de forma gratuita, inmediata y recurrente recursos psicoeducativos para prevenir la violencia de género y fomentar relaciones sanas.</t>
+          <t>Plataforma digital que mediante un chatbot con inteligencia artificial, ofrece de forma gratuita, inmediata y recurrente recursos psicoeducativos para prevenir la violencia de género y fomentar relaciones sanas. Su misión es convertirse en la plataforma sostenible y multidisciplinaria líder, proporcionando tecnologías escalables y expertos que guíen a las personas hacia relaciones libres de violencia.</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1677,7 +1671,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -1698,11 +1692,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1745,7 +1739,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi.</t>
+          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el contenido de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento punteral (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. importante: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -1769,7 +1763,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Amplio uso durante la pandemia para evaluación temprana de casos. Facilitó la detección y canalización de pacientes COVID, reduciendo la carga en centros de salud.</t>
+          <t>Amplio uso durante la pandemia para evaluación temprana de casos. Facilitó la detección y canalización de pacientes COVID, reduciendo la carga en centros de salud. Reconocido como ejemplo regional de IA aplicada a emergencias sanitarias​oecd.org​oecd.org.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1784,7 +1778,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
@@ -1805,11 +1799,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1876,7 +1870,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Permite consultar CV y antecedentes de candidatos y reporte de irregularidades.</t>
+          <t>Permite consultar cv y antecedentes de candidatos y reporte de irregularidades.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1891,7 +1885,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
@@ -1940,11 +1934,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1987,7 +1981,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>El Laboratorio de Aceleración (AccLab) del PNUD Paraguay, junto con estudiantes de la Escuela de Políticas Públicas (SIPA) de la Universidad de Columbia (Nueva York), la Dirección de Innovación del MITIC y el equipo global de l…</t>
+          <t>El Laboratorio de Aceleración (AccLab) del PNUD Paraguay, junto con estudiantes de la Escuela de Políticas Públicas (sipa) de la Universidad de Columbia (Nueva York), la Dirección de Innovación del mitic y el equipo global de los Laboratorios de Aceleración, puso a prueba una metodología participativa para realizar consultas ciudadanas sobre IA en Paraguay (2024-2025). Se recogieron aportes mediante consultas callejeras, grupos focales, encuestas en línea y entrevistas con actores diversos (estudiantes, docentes, jóvenes, autoridades, especialistas en tecnología, trabajadores de sectores populares y adultos de Asunción y otras ciudades). Los resultados (p. ej. brecha urbano-rural en la percepción de la IA y correlación ingreso-optimismo) fueron insumo del diagnóstico aila (Artificial Intelligence Landscape Assessment / Atlas de IA). El objetivo del piloto fue desarrollar una metodología estandarizada, replicable, para generar datos agregables y comparables a escala regional/global; la base anonimizada de encuestas callejeras y digitales se publicó en formato xls en Zenodo.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2002,7 +1996,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA </t>
+          <t>El criterio elegible exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) sobre el contenido de los aportes. Aquí ocurre lo contrario: la IA es el tema de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y el análisis de los aportes es de encuestas/mixed-methods tradicional: recoleccion via formularios (Microsoft Forms en la metodologia aila estandar), base de datos estructurada publicada en xls en Zenodo, puntajes ponderados y visualizacion (Power bi), con hallazgos presentados como cruces y correlaciones estadisticas (brecha urbano-rural; a mayor ingreso, mayor optimismo) y sintesis cualitativa de grupos focales/entrevistas. Se verifico especificamente la pista del equipo (¿se uso NLP/sentimiento/clustering o herramienta tipo Citibeats?) y no se hallo ninguna evidencia de ello en el blog del PNUD, en los reportes aila/nota metodologica ni en la prensa secundaria (La Tribuna, Foco/La Nacion, Forbes). Por tanto el analisis es cualitativo/estadistico tradicional y la IA solo es el tema =&gt; Confianza no maxima porque el blog PNUD y el pdf aila devolvieron http 403 a WebFetch/curl (proxy) y las citas verbatim se reconstruyeron via WebSearch; no obstante, multiples busquedas convergentes coinciden y ninguna menciona NLP sobre los aportes.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
@@ -2015,7 +2009,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Recomendador de ofertas y capacitaciones que alinea CV con demanda empresarial.</t>
+          <t>Recomendador de ofertas y capacitaciones que alinea cv con demanda empresarial.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -2030,7 +2024,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
@@ -2051,11 +2045,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2126,11 +2120,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2173,7 +2167,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MP…</t>
+          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (idb). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo no viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking depende del plan contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras de investigacion (&gt;=14 busquedas/fetches) no se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el contenido de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, excluido del criterio).</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2186,7 +2180,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Caso borde: el chatbot AskNDTS (IA) informa/apoya la implementación del proceso NDTS y el módulo Go Vocal Sensemaking está planeado (existe). como apoyo a la implementación.</t>
+        </is>
+      </c>
       <c r="F2" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2205,11 +2203,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2252,7 +2250,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Chatbot oficial de la Ciudad Autónoma de Buenos Aires, diseñado para acercar información y trámites municipales a los vecinos mediante WhatsApp y otros canales digitales Buenos Aires.</t>
+          <t>Chatbot oficial de la Ciudad Autónoma de Buenos Aires, diseñado para acercar información y trámites municipales a los vecinos mediante WhatsApp y otros canales digitales Buenos Aires. Su objetivo inicial fue ofrecer respuestas precisas en ámbitos específicos antes de expandirse a múltiples temas de la ciudad. A lo largo de su operación, ha evolucionado incorporando tecnologías de inteligencia artificial generativa y módulos especializados para atender desde consultas turísticas hasta denuncias por violencia laboral.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2267,7 +2265,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
@@ -2295,7 +2293,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
@@ -2323,7 +2321,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA</t>
+          <t>No se identifica uso de IA.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
@@ -2336,7 +2334,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Algoritmo que cruza datos demográficos, inmobiliarios y POS para recomendar zonas de inversión a pymes.</t>
+          <t>Algoritmo que cruza datos demográficos, inmobiliarios y pos para recomendar zonas de inversión a pymes.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2351,7 +2349,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>No entra en la descripción de lo que es Participación ciudadana. Se considera Civic Tech, pero no participación ciudadana</t>
+          <t>En la descripción de lo que es Participación ciudadana. Se considera Civic Tech, pero no participación ciudadana.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
@@ -2379,7 +2377,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>No entra en la descripción de lo que es Participación ciudadana. Se considera Civic Tech, pero no participación ciudadana. Tampoco utiliza IA</t>
+          <t>En la descripción de lo que es Participación ciudadana. Se considera Civic Tech, pero no participación ciudadana. Tampoco utiliza IA.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
@@ -2400,11 +2398,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2447,7 +2445,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC).</t>
+          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2471,7 +2469,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Asistente Virtual de AGESIC – Chatbot gubernamental piloto lanzado en 2018 para adquirir experiencia en soluciones de IA en la atención ciudadana.</t>
+          <t>Asistente Virtual de agesic – Chatbot gubernamental piloto lanzado en 2018 para adquirir experiencia en soluciones de IA en la atención ciudadana. Entrenado con preguntas frecuentes recibidas en los distintos canales de contacto del Estado​oecd.org. No solo contesta consultas de trámites, sino que puede ejecutar acciones (ej. reestablecer contraseña de usuario) para resolver problemas comunes​oecd.org. Integrado en la estrategia multicanal de atención, buscando acercar el Estado a la gente eliminando barreras de acceso.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -2486,7 +2484,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
@@ -2499,7 +2497,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Es una iniciativa del gobierno uruguayo para definir una política pública de IA que abarque los sectores público, privado, académico y de la sociedad civil.</t>
+          <t>Es una iniciativa del gobierno uruguayo para definir una política pública de IA que abarque los sectores público, privado, académico y de la sociedad civil. Su objetivo es fomentar el desarrollo y uso ético, responsable y seguro de la IA, promoviendo el crecimiento económico inclusivo, la sostenibilidad ambiental y el fortalecimiento de la soberanía nacional.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2514,7 +2512,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No evidencia de uso de IA.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
@@ -2527,7 +2525,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Consulta pública nacional y participación multiactores impulsada por el Parlamento de Uruguay junto a Agesic, el Consejo Nacional Consultivo Honorario de los Derechos de la Niñez y la Adolescencia, Ceibal, UNICEF y PNUD.</t>
+          <t>Consulta pública nacional y participación multiactores impulsada por el Parlamento de Uruguay junto a Agesic, el Consejo Nacional Consultivo Honorario de los Derechos de la Niñez y la Adolescencia, Ceibal, UNICEF y PNUD. Recoge experiencias, propuestas y perspectivas de la ciudadanía, la academia, la sociedad civil y, de manera central, de las propias niñas, niños y adolescentes, sobre el impacto de los entornos digitales y la inteligencia artificial en la infancia y adolescencia. Combina tres modalidades: consulta abierta digital vía la Plataforma de Participación Ciudadana Digital (Decidim), mesas de intercambio multiactor e instancias específicas para nna. El objetivo es generar información pública de calidad para la agenda legislativa (antes de legislar, escuchar). nota: la IA es el tema/objeto de la consulta, no necesariamente una herramienta de procesamiento de los aportes.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2542,7 +2540,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el</t>
+          <t>Temporal: la consulta está abierta hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis no se ha ejecutado, por lo que un eventual uso de IA sobre el contenido de los aportes no está demostrado ni desplegado. sustantivo: no se halló ninguna evidencia textual de que se use IA/NLP/ML/clustering para clasificar, agrupar, resumir o analizar el contenido de los aportes ciudadanos. Las descripciones oficiales del proceso (Agesic, misma Plataforma de Participación Ciudadana Digital / Decidim) apuntan a análisis humano por equipos técnicos ('los aportes recibidos se sistematizan y, analizada su viabilidad por equipos técnicos, se utilizan como insumos'; 'según su pertinencia, viabilidad y prioridad'), y el producto es un 'documento de síntesis' agregado. El precedente directo (Consulta Pública Estrategia Nacional de IA, uy, ya listado y excluido por 'No evidencia de uso de IA') usó análisis humano en esta misma plataforma. La IA es el tema/objeto de la consulta (impacto de la IA en la infancia), no una herramienta de procesamiento de los aportes. Por criterio (consulta abierta sin fase de análisis ejecutada + sin evidencia de IA sobre los aportes) -&gt; no.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
@@ -2563,11 +2561,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2610,7 +2608,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Proceso de consulta/debate para la elaboración del Plan de la Patria de las 7 Grandes Transformaciones (7T) 2025-2031, conducido por el Gobierno Bolivariano de Venezuela (Ministerio del Poder Popular de Planificación / Vicepres…</t>
+          <t>Proceso de consulta/debate para la elaboración del Plan de la Patria de las 7 Grandes Transformaciones (7T) 2025-2031, conducido por el Gobierno Bolivariano de Venezuela (Ministerio del Poder Popular de Planificación / Vicepresidencia). Durante ~2 meses se desplegó un proceso de debate sectorial y territorial con opción de propuesta individual, mediante más de 63.000 asambleas de base. Según fuentes oficiales: 3.437.434 participantes registrados vía Carnet de la Patria, 33.780 relatores/sistematizadores registrados en un portal para la sistematización de propuestas, y 34.491 propuestas procesadas/cargadas. La metodología oficial documentada (sistema web hagamospatria.org.ve + transcriptores para aportes físicos) establece que el relator sistematiza las propuestas concretas de la mesa 'validando con los participantes', con tres niveles de agregación (nacional, estadal, base) y revisión 'una por una' por el equipo de sistematización 'con el apoyo de herramientas informáticas especializadas', clasificando los aportes en cuatro categorías (propuestas generales, propuestas concretas, modificaciones de redacción del Plan y otra información como denuncias/solicitudes). La asistencia se georreferenció con aplicaciones de código qr del Carnet de la Patria, construyéndose un Sistema de Información Geográfica (sig) con base de datos de propuestas y asambleas. señal dudosa (resuelta ): prensa estatal (Correo del Orinoco, mar-2026; replicado por fevp.gob.ve, mincyt.gob.ve, cendit.gob.ve, mppre.gob.ve y laprensademonagas.com) afirma que el Plan 'ha procesado más de 500.000 propuestas... usando herramientas de IA y Big Data para generar los algoritmos'. En paralelo, y como eje temático del plan, Maduro instruyó 'incluir la Inteligencia Artificial en el Plan de las 7T' como prioridad nacional (de ahí derivan el Plan Nacional de IA, el Código de Ética de IA feb-2026 y el Proyecto de Ley de IA), lo que no equivale a IA analizando el contenido de los aportes ciudadanos de la consulta.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2625,208 +2623,13 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 prop</t>
+          <t>No (resuelto en , antes duda). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo contenido sí fue recolectado, cargado, sistematizado y agrupado. Pero la confirma que el actor del análisis fue humano + herramientas informáticas de clasificación + sig, no IA: la metodología oficial (corroborada en múltiples resultados que indexan el documento del Plan 7T) describe que las propuestas fueron 'revisadas una por una por el equipo de sistematización, con el apoyo de herramientas informáticas especializadas' y clasificadas en cuatro categorías, y que 'el relator sistematiza las propuestas concretas de la mesa validando con los participantes', con tres niveles de agregación. La única afirmación de que 'IA y Big Data procesaron 500.000+ propuestas' sigue proviniendo solo de prensa estatal/oficialista (Correo del Orinoco y mirrors mincyt, Cendit, fevp, mppre, más un diario regional), sin proveedor, sin descripción técnica (ningún modelo, NLP, ML, clustering), contradiciendo la cifra oficial verificable (34.491) y con la coletilla 'para generar los algoritmos' que apunta a la IA como producto del Plan Nacional de IA, no como herramienta sobre los aportes. no se halló ninguna corroboración técnica independiente (proveedor de software, paper académico, documento técnico, organismo) tras 6-10 búsquedas dirigidas; fuentes críticas/académicas (Small Wars Journal/asu, Data Big and Small, GISWatch, Bentata) tratan la agenda de IA soberana y la infraestructura de datos, pero ninguna corrobora IA sobre las propuestas de la consulta. Adicionalmente, 'incluir la IA en el Plan de las 7T' describe a la IA como eje temático/prioridad del plan; por la regla del índice, eje temático ≠ elegibilidad. Conclusión binaria: no, por ausencia de corroboración técnica creíble de IA (NLP/ML) procesando el contenido de las propuestas. Dato verificable que queda en su lugar: 34.491 propuestas sistematizadas por relatores humanos + herramientas de clasificación + sig. url de prensa estatal marcada en gaps para revisión manual.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Caso</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Descripción breve</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Fuente (URL validada)</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>¿Se incluye?</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Motivo (si NO/DUDA)</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Comentario / corrección (partner)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>CAF invirtió en la startup govtech OS City para acelerar la digitalización de trámites y la emisión de credenciales oficiales con blockchain e IA, impulsando su expansión regional.</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>No es participación ciudadana</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Botivist</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Botivist es una iniciativa de Microsoft Research que usa inteligencia artificial para promover la participación ciudadana en causas sociales.</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>No tiene foco en un país específico</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Chatbot web que guía a la ciudadanía para formular y encauzar denuncias de corrupción ante las Entidades Fiscalizadoras Superiores (EFS) de los cuatro países participantes</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>No evidencia de uso de IA</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Escucha social de opiniones en Twitter y foros para detectar temas, sentimiento y desinformación sobre salud, empleo, educación, etc., generando alertas para ajustar la comunicación pública.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Análisis de redes sociales, no es participación</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Ushahidi "AI for Good"</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Es una plataforma digital de código abierto creada en 2008 para recopilar y mapear información enviada por ciudadanos en contextos como elecciones, crisis o desastres.</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ushahidi.com/</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2841,11 +2644,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2888,7 +2691,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Plataforma de diálogo digital que emplea IA para procesar y agrupar aportaciones ciudadanas en tiempo real, retornando feedback inmediato y garantizando anonimato, con vistas a fomentar el reencuentro y la cohesión social en el…</t>
+          <t>Plataforma de diálogo digital que emplea IA para procesar y agrupar aportaciones ciudadanas en tiempo real, retornando feedback inmediato y garantizando anonimato, con vistas a fomentar el reencuentro y la cohesión social en el país.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2920,11 +2723,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2967,7 +2770,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Proceso participativo de consulta pública nacional para la construcción de la nueva Estrategia Nacional de Ciencia, Tecnología e Innovación (ENCTI 2030).</t>
+          <t>Proceso participativo de consulta pública nacional para la construcción de la nueva Estrategia Nacional de Ciencia, Tecnología e Innovación (encti 2030). Comprendió más de 200 etapas preparatorias (18 reuniones temáticas, 157 conferencias libres, 27 conferencias estaduales, 14 municipales y 5 regionales), con más de 100 mil participantes en 221 eventos, culminando en la etapa nacional en Brasília (30-31 jul y 1 ago 2024). La Subcomissão de Sistematização e Documentação usó IA para transcribir, analizar, sistematizar y sintetizar las contribuciones, produciendo e-books de síntesis y los Libros Lilás (rec. de la sociedad) y Violeta (documento de referencia) que orientan la encti.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2991,7 +2794,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Brasil Participativo es la plataforma digital de participación social del Gobierno Federal de Brasil (construida sobre el software libre Decidim), lanzada en 2023 por la Secretaria-Geral da Presidência da República.</t>
+          <t>Brasil Participativo es la plataforma digital de participación social del Gobierno Federal de Brasil (construida sobre el software libre Decidim), lanzada en 2023 por la Secretaria-Geral da Presidência da República. En ella la ciudadanía envía propuestas de texto libre, revisiones, comentarios y votos sobre políticas públicas en procesos participativos federales reales: el Plano Plurianual Participativo (PPA 2024-2027), el Plano Clima Participativo y el Congresso da Juventude, además de conferencias y consultas públicas. Sobre el contenido de esas propuestas, equipos de la Universidade de Brasília (lappis/fga-UnB) y la Residência TIC brisa desarrollaron un pipeline de IA que recolecta, clasifica y agrupa por temas las propuestas: combina modelado de tópicos con BERTopic (probando varios embeddings: BERTimbau, LaBSE, GovBERT-br, etc.), incorpora conocimiento institucional mediante seed words extraídas del vcge (Vocabulário Controlado do Governo Eletrônico) y usa LLMs para el etiquetado/validación automática de los tópicos, generando categorías y reportes temáticos consistentes con la taxonomía oficial para apoyar a los equipos de formulación de políticas. Se documenta un pipeline ML en evolución hacia producción (paper 'From Pre-labeling to Production') y un clasificador ML adicional (bp-Classificador-de-Propostas) entrenado a diario con Apache Airflow con datos de la plataforma, descrito como destinado a integrarse en la plataforma.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -3015,7 +2818,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Colab es una plataforma GovTech que permite a los ciudadanos reportar problemas urbanos, sugerir ideas, participar en encuestas y votar en decisiones municipales.</t>
+          <t>Colab es una plataforma GovTech que permite a los ciudadanos reportar problemas urbanos, sugerir ideas, participar en encuestas y votar en decisiones municipales. Utiliza IA para optimizar la gestión pública, automatizar procesos y mejorar la eficiencia en la prestación de servicios públicos. Entre los servicios que ofrece están las consultas.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -3028,7 +2831,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Permite sugerir ideas y votar en decisiones municipales (módulos de participación).</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -3039,7 +2846,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Investigación académica (Co:Lab USP / Cátedra Brasil-Alemania, GETIP) sobre el uso de IA generativa para apoyar a la ciudadanía a redactar y estructurar propuestas en procesos de participación, tomando como referencia el orçame…</t>
+          <t>Investigación académica (Co:Lab USP / Cátedra Brasil-Alemania, getip) sobre el uso de IA generativa para apoyar a la ciudadanía a redactar y estructurar propuestas en procesos de participación, tomando como referencia el orçamento participativo de São Paulo. Descrito como 'pesquisas em andamento' / proyecto de investigación-prototipo, no como una herramienta oficial desplegada en el proceso real (que opera vía la plataforma Participe+/Participe Mais de la Prefeitura, sin IA generativa confirmada).</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3063,7 +2870,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>OPA (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (SEPLAN) con apoyo de la Secretaria de …</t>
+          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3087,7 +2894,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029</t>
+          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3135,7 +2942,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (PAS) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), platafor…</t>
+          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3159,7 +2966,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes.</t>
+          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3187,7 +2994,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Brasil Participativo es la plataforma digital de participación social del Gobierno Federal de Brasil, construida sobre el software libre Decidim y lanzada en 2023 por la Secretaria Nacional de Participação Social (Secretaria-Ge…</t>
+          <t>Brasil Participativo es la plataforma digital de participación social del Gobierno Federal de Brasil, construida sobre el software libre Decidim y lanzada en 2023 por la Secretaria Nacional de Participação Social (Secretaria-Geral da Presidência da República). El repositorio bp-Classificador-de-Propostas (Residência TIC brisa, en alianza con UnB-Gama/fga y lappis) es un componente de IA que hace 'Indexação Automática com ML das propostas publicadas no Brasil Participativo': un modelo de clasificación (scikit-learn/nltk) reentrenado a diario con Apache Airflow sobre los datos de la plataforma, expuesto como servicio Python + una gema Ruby ('proposal-classifier') para integrarse a plataformas web 'afim de ser integrado a plataforma do Brasil Participativo'. Este componente es el mismo esfuerzo de indexación/clasificación de propuestas ya documentado en la ficha br-brasil-participativo-clustering-semantic (que cita este mismo repositorio y los papers arXiv 2509.21292 -clustering semántico BERTopic+LLM- y 2511.01545 -'From Pre-labeling to Production', lecciones de ingeniería del pipeline ML en el sector público- como su evidencia).</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3202,7 +3009,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>NO ENTRA POR DOBLE CONTEO. Este candidato (BP-Classificador-de-Propostas, Residência TIC BRISA / UnB-FGA / LAPPIS) es el MISMO caso ya contabilizado en la ficha BR-brasil-participativo-clustering-sema</t>
+          <t>Por doble conteo. Este candidato (bp-Classificador-de-Propostas, Residência TIC brisa / UnB-fga / lappis) es el mismo caso ya contabilizado en la ficha br-brasil-participativo-clustering-semantic, no un caso distinto. Prueba directa: (a) esa ficha ya cita este mismo repositorio (https://github.com/ResidenciaTICBrisa/bp-Classificador-de-Propostas) como una de sus fuentes (estado ok) y lo describe explícitamente; (b) su alerta de alcance reconoce 'al menos dos artefactos de IA relacionados pero distintos: (a) el pipeline de clustering semántico BERTopic+LLM (papers) y (b) el clasificador supervisado ML bp-Classificador-de-Propostas (scikit-learn/Airflow, GitHub). Ambos operan sobre las propuestas de Brasil Participativo y comparten autores/laboratorio; se documentan juntos en esta ficha por pertenecer al mismo esfuerzo de indexación/clasificación de aportes'; (c) los papers que sustentan la ficha contada (arXiv 2509.21292 'Semantic Clustering' y 2511.01545 'From Pre-labeling to Production') son la producción académica de este mismo equipo y describen la evolución de este mismo clasificador. Es, por tanto, un componente/duplicado del caso Brasil Participativo ya contado, no un despliegue independiente en un proceso participativo distinto. Adicionalmente, el criterio de producción tampoco se cumple: la integración a la plataforma oficial se describe como intención ('afim de ser integrado a plataforma do Brasil Participativo'), no como despliegue confirmado; no se halló fuente gubernamental que confirme el clasificador operando en producción (el relanzamiento oficial de 15/08/2025 no menciona clasificación automática por IA). Se distingue del pipeline BERTopic (arXiv 2509.21292) solo como su arm de 'clasificación supervisada', pero ambos pertenecen al mismo caso ya listado. Veredicto: no (doble conteo con br-brasil-participativo-clustering-semantic).</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -3215,7 +3022,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>El Gobierno de Brasil ha lanzado una nueva funcionalidad de búsqueda por voz en el portal GOV.BR, permitiendo a los usuarios acceder a más de 4.300 servicios digitales mediante comandos de voz.</t>
+          <t>El Gobierno de Brasil ha lanzado una nueva funcionalidad de búsqueda por voz en el portal gov.br, permitiendo a los usuarios acceder a más de 4.300 servicios digitales mediante comandos de voz. Esta iniciativa, busca facilitar la ciudadanía digital, especialmente para personas con discapacidad visual o dificultades para escribir.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3230,7 +3037,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -3243,7 +3050,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Iniciativa del Senado Federal de Brasil que busca potenciar la participación ciudadana en el proceso legislativo mediante el uso de inteligencia artificial.</t>
+          <t>Iniciativa del Senado Federal de Brasil que busca potenciar la participación ciudadana en el proceso legislativo mediante el uso de inteligencia artificial. El propósito principal es transformar a los ciudadanos de votantes ocasionales en participantes activos en la creación de leyes, utilizando herramientas digitales y IA para facilitar y enriquecer su involucramiento en el proceso legislativo.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -3258,7 +3065,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Propuesta, pero no hay datos sobre que se vaya a ejecutar</t>
+          <t>Propuesta, pero no hay datos sobre que se vaya a ejecutar.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -3286,7 +3093,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -3299,7 +3106,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Secretario virtual basado en IA que guía a los ciudadanos a través de la Guía de Servicios digital del estado (portal unificado de trámites).</t>
+          <t>Secretario virtual basado en IA que guía a los ciudadanos a través de la Guía de Servicios digital del estado (portal unificado de trámites). Extrae información vía API de un catálogo centralizado y responde consultas ciudadanas sobre requisitos, horarios, ubicaciones y pasos para acceder a servicios públicos​oecd.org​oecd.org. Objetivo: mejorar la experiencia ciudadana en trámites, ofreciendo atención 24/7 y estandarizada.</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3314,7 +3121,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -3327,7 +3134,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Es una plataforma digital desarrollada por el Instituto de Tecnología y Sociedad de Río (ITS Rio) para facilitar la creación y firma de proyectos de ley de iniciativa popular mediante el uso de tecnología blockchain, que garant…</t>
+          <t>Es una plataforma digital desarrollada por el Instituto de Tecnología y Sociedad de Río (its Rio) para facilitar la creación y firma de proyectos de ley de iniciativa popular mediante el uso de tecnología blockchain, que garantiza la seguridad y verificabilidad de las firmas digitales.</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3342,7 +3149,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA</t>
+          <t>No se identifica uso de IA.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -3355,7 +3162,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ParticipAct es una plataforma brasileña de ciencia ciudadana de código abierto que permite a los ciudadanos reportar problemas urbanos directamente a las agencias públicas a través de una aplicación web y móvil.</t>
+          <t>ParticipAct es una plataforma brasileña de ciencia ciudadana de código abierto que permite a los ciudadanos reportar problemas urbanos directamente a las agencias públicas a través de una aplicación web y móvil. Utiliza inteligencia artificial para facilitar el registro de los reportes, analizar los datos y mejorar la comunicación con el público mediante chatbots, con el fin de fomentar la colaboración para resolver los problemas de la ciudad.</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -3383,7 +3190,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Participa + Brasil es una plataforma oficial del Gobierno Federal de Brasil que centraliza oportunidades de participación social, como consultas públicas, audiencias y consejos, permitiendo a los ciudadanos contribuir en la for…</t>
+          <t>Participa + Brasil es una plataforma oficial del Gobierno Federal de Brasil que centraliza oportunidades de participación social, como consultas públicas, audiencias y consejos, permitiendo a los ciudadanos contribuir en la formulación de políticas públicas.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3398,7 +3205,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA</t>
+          <t>No se identifica uso de IA.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -3411,7 +3218,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>El artefacto NO opera un proceso participativo propio: es una aplicación cliente que recolecta (web scraping) los contenidos públicos de la plataforma federal Brasil Participativo (propuestas, planes y conferencias) y los prese…</t>
+          <t>El artefacto no opera un proceso participativo propio: es una aplicación cliente que recolecta (web scraping) los contenidos públicos de la plataforma federal Brasil Participativo (propuestas, planes y conferencias) y los presenta de forma mas accesible. Los procesos participativos subyacentes son los de Brasil Participativo (Secretaria-Geral da Presidencia / Secretaria Nacional de Participacao Social), que ya estan cubiertos por la ficha br-brasil-participativo-clustering-semantic. Participe+ es un proyecto de la disciplina mds (Metodos de Desenvolvimento de Software) de Ingenieria de Software de la Universidade de Brasilia (organizacion GitHub unb-mds), semestre 2025.1, con release v1.0.0 (09/07/2025). No es la plataforma oficial ni el pipeline oficial de IA de lappis/brisa; es un desarrollo estudiantil independiente construido sobre los datos de Brasil Participativo.</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3426,7 +3233,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>NO ENTRA. Aunque tecnicamente la IA SI procesa el CONTENIDO de los aportes (agrupa por temas via HDBSCAN y clasifica en eixos por similitud semantica, ademas de resumir con LLM), el candidato incumple</t>
+          <t>Aunque tecnicamente la IA si procesa el contenido de los aportes (agrupa por temas via hdbscan y clasifica en eixos por similitud semantica, ademas de resumir con LLM), el candidato incumple una condicion necesaria del criterio de inclusion ('si solo si caso distinto, desplegado oficialmente'): no hay despliegue oficial ni adopcion por la Secretaria Nacional de Participacao Social; es un ejercicio de la disciplina mds (Ingenieria de Software, UnB, org unb-mds, semestre 2025.1) con release v1.0.0 del 09/07/2025 y unico 'deploy' un sitio de documentacion en GitHub Pages, patron tipico de proyecto academico de un semestre, sin usuarios reales ni operacion gubernamental. substancial solapamiento con el caso ya contado br-brasil-participativo-clustering-semantic: opera sobre la misma plataforma Brasil Participativo (raspa sus propuestas), pertenece al mismo ecosistema UnB y replica la misma idea de clustering/clasificacion tematica de propuestas, pero como artefacto estudiantil paralelo, no como el pipeline oficial de lappis/brisa. Se distingue del municipal 'Participe+' de la Prefeitura de Sao Paulo (participemais.prefeitura.sp.gov.br), que es otro caso no relacionado. Por incumplir 'desplegado oficialmente' (ejercicio estudiantil sin adopcion) y por solapar con el caso federal ya contado, la decision es no. La duda central (¿va mas alla de resumir?) se resuelve a favor de 'si procesa contenido', pero eso no basta para entrar sin despliegue oficial.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -3439,7 +3246,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>El proceso participativo real subyacente es Brasil Participativo, la plataforma digital de participación social del Gobierno Federal de Brasil (construida sobre Decidim, lanzada en 2023 por la Secretaria-Geral da Presidência da…</t>
+          <t>El proceso participativo real subyacente es Brasil Participativo, la plataforma digital de participación social del Gobierno Federal de Brasil (construida sobre Decidim, lanzada en 2023 por la Secretaria-Geral da Presidência da República), donde la ciudadanía envía propuestas de texto libre, comentarios y votos sobre políticas públicas (PPA Participativo, Plano Clima, etc.). Projeto Lumina no es ese proceso ni un componente oficial de él: es un proyecto de software desarrollado por estudiantes en la disciplina 'Métodos de Desenvolvimento de Software' (mds) del curso de Engenharia de Software de la Universidade de Brasília (UnB-fga), semestre 2024-2, que aplica análisis de sentimiento (positivo/negativo/neutro) sobre las propuestas/comentarios de los Planos Participativos publicados en Brasil Participativo. Es un ejercicio académico (una webapp con documentación MkDocs y 'Versão Final' de fin de curso en feb-2025), no un despliegue oficial.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -3454,7 +3261,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>NO ENTRA. Aunque la IA sí actúa sobre el CONTENIDO de aportes ciudadanos (análisis de sentimiento positivo/negativo/neutro de las propuestas y comentarios de Brasil Participativo, rol_IA=contenido), f</t>
+          <t>Aunque la IA sí actúa sobre el contenido de aportes ciudadanos (análisis de sentimiento positivo/negativo/neutro de las propuestas y comentarios de Brasil Participativo,, falla el requisito de despliegue oficial: Projeto Lumina es un ejercicio académico de la disciplina 'Métodos de Desenvolvimento de Software' del curso de Engenharia de Software de la UnB (semestre 2024-2), no un sistema adoptado ni operado por el gobierno. La señal del candidato conflaciona 'mds' (el nombre de la disciplina y de la org GitHub 'unb-mds') con 'Ministério do Desenvolvimento Social': no se halló evidencia de asociación oficial con ese Ministerio ni con la Secretaria Nacional de Participação Social, ni de integración en producción. El repositorio sigue el patrón idéntico de decenas de proyectos estudiantiles de 'unb-mds' (DFemObras, SuaGradeUnB, LicitaBSB, forUnB, GovInsights, etc.), tiene 3 stars/4 forks y su 'Versão Final' (feb-2025) marca el fin del curso. Sobre el doble conteo: no es un componente ni duplicado técnico de la ficha ya contada 'Brasil Participativo - clustering semántico' (esa es el pipeline oficial BERTopic+LLM de lappis/brisa con mentoría de la Secretaria de Participação Social); Lumina es un artefacto distinto (webapp estudiantil que consume datos de bp), pero igualmente inelegible por ser académico sin adopción. Conclusión: no por ejercicio académico sin despliegue oficial.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -3467,7 +3274,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Querido Diário es una plataforma de Open Knowledge Brasil que emplea inteligencia artificial para clasificar, contextualizar y expandir la información de los diarios oficiales municipales, haciéndolos accesibles en formato abie…</t>
+          <t>Querido Diário es una plataforma de Open Knowledge Brasil que emplea inteligencia artificial para clasificar, contextualizar y expandir la información de los diarios oficiales municipales, haciéndolos accesibles en formato abierto y amigable. Al centralizar más de 850.000 diarios de 522 municipios, facilita el monitoreo ciudadano de actos oficiales y promueve el control social mediante búsquedas semánticas y una API abierta que integra estos datos en otras herramientas cívicas.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3482,7 +3289,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
@@ -3495,7 +3302,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Robô ALICE es una herramienta de inteligencia artificial desarrollada por la CGU para automatizar el análisis de datos en procesos de compras públicas, permitiendo identificar patrones y posibles irregularidades en la administr…</t>
+          <t>Robô alice es una herramienta de inteligencia artificial desarrollada por la CGU para automatizar el análisis de datos en procesos de compras públicas, permitiendo identificar patrones y posibles irregularidades en la administración pública.</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -3510,7 +3317,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -3523,7 +3330,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Serenata.ai es el sitio web oficial de la Operación Serenata de Amor, un proyecto brasileño de innovación cívica.</t>
+          <t>Serenata.ai es el sitio web oficial de la Operación Serenata de Amor, un proyecto brasileño de innovación cívica. Su objetivo principal es fiscalizar el uso de fondos públicos por parte de diputados y senadores, utilizando técnicas de IA para detectar posibles irregularidades en los reembolsos solicitados por los parlamentarios.</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3538,7 +3345,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>No es participación Ciudadana</t>
+          <t>No es participación Ciudadana.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
@@ -3566,7 +3373,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
@@ -3587,11 +3394,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3634,7 +3441,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Análisis de los cabildos del proceso constitucional en 2016</t>
+          <t>Análisis de los cabildos del proceso constitucional en 2016.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -3658,7 +3465,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el est…</t>
+          <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el estallido social. Entre noviembre de 2019 y marzo de 2020, la ciudadanía pudo participar mediante diálogos grupales (cabildos) o consultas individuales en el sitio www.chilequequeremos.cl, registrando sus necesidades y propuestas para complementar futuras políticas públicas. El proceso fue un esfuerzo conjunto de los Ministerios de Desarrollo Social y Familia, de Ciencia/Tecnología/Conocimiento e Innovación (MinCiencia), de Agricultura, la segegob y la División de Gobierno Digital. El Ministerio de Ciencia fue responsable de sistematizar los aportes ciudadanos usando ciencia de datos / IA: el repositorio público MinCiencia/ECQQ contiene el código que clasifica las contribuciones (texto libre de los aportes) mediante redes neuronales recurrentes (rnn) y árboles de decisión (Random Forest), y sistematiza emociones y necesidades mediante análisis de tópicos (NLP/lda) sobre el contenido de diálogos y consultas individuales.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -3695,7 +3502,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -3706,7 +3517,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena</t>
+          <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3743,7 +3554,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Jornada de escucha / diálogo — proceso ejecutado por el equipo (confirmado).</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
@@ -3754,7 +3569,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S.</t>
+          <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S. Fishkin) convocada por el Senado de Chile (Comisión Desafíos del Futuro) junto a la Fundación Tribu, el Centro para la Democracia Deliberativa de la Universidad de Stanford, la Universidad de Chile, la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil. Un mini-público de ~400-514 ciudadanos seleccionados aleatoriamente y representativos del país deliberó de forma online (vía Zoom y la Stanford Online Deliberation Platform) los días 5, 6 y 7 de marzo de 2021 sobre reformas a pensiones y salud, en grupos pequeños y sesiones plenarias, de cara al debate constitucional. El proceso comenzó en diciembre de 2020 con la selección de la muestra y la entrega de material informativo equilibrado (argumentos a favor y en contra). La plataforma online de Stanford incorporó un moderador automatizado (IA) que controlaba los tiempos y distribuía equitativamente los turnos de palabra (colas de habla, temporizador, sistema de señal para determinar quién hablaba a continuación); en paralelo, el Centro de Microdatos de la U. de Chile usó tecnología basada en IA para seleccionar la muestra representativa.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3767,7 +3582,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Mini-público del Senado; la IA modera y administra los turnos de palabra (Implementación/Planificación).</t>
+        </is>
+      </c>
       <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
@@ -3791,7 +3610,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Consulta a nuevos votantes con NLP — proceso ejecutado por el equipo (confirmado).</t>
+        </is>
+      </c>
       <c r="F8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -3802,7 +3625,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional</t>
+          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3826,7 +3649,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogo y participación llevada a cabo por la UCH y PUC en el contexto de manifestaciones sociales</t>
+          <t>Iniciativa de diálogo y participación llevada a cabo por la uch y puc en el contexto de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3874,7 +3697,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>El Proyecto CAMINAR (Cámara Inteligencia Artificial) es una iniciativa de la Cámara de Diputadas y Diputados de Chile que busca modernizar el trabajo parlamentario mediante el uso de inteligencia artificial.</t>
+          <t>El Proyecto caminar (Cámara Inteligencia Artificial) es una iniciativa de la Cámara de Diputadas y Diputados de Chile que busca modernizar el trabajo parlamentario mediante el uso de inteligencia artificial. El proyecto tiene como objetivo mejorar la eficiencia, transparencia y accesibilidad de los procesos legislativos.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3889,7 +3712,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>De acuerdo a la descripción, solo permitiría a los ciudadanos consultar</t>
+          <t>De acuerdo a la descripción, solo permitiría a los ciudadanos consultar.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -3902,7 +3725,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Investigación que desarrolló un modelo de inteligencia artificial para inferir automáticamente las posturas políticas de los usuarios de Twitter durante los procesos constitucionales de 2020 y 2022.</t>
+          <t>Investigación que desarrolló un modelo de inteligencia artificial para inferir automáticamente las posturas políticas de los usuarios de Twitter durante los procesos constitucionales de 2020 y 2022. Este modelo, basado en redes neuronales convolucionales sobre grafos (Graph Convolutional Networks), analiza tanto el contenido textual de los tuits como las conexiones entre usuarios y temas para predecir si un usuario apoya o rechaza una propuesta constitucional.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -3917,7 +3740,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Es un estudio</t>
+          <t>Es un estudio.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -3930,7 +3753,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Modelo de gestión presupuestaria deliberativa y vinculante de la Municipalidad de Pudahuel (presupuesto municipal 2023): participación virtual abierta + grupos de especial protección; +1.200 participantes y 150+ iniciativas de …</t>
+          <t>Modelo de gestión presupuestaria deliberativa y vinculante de la Municipalidad de Pudahuel (presupuesto municipal 2023): participación virtual abierta + grupos de especial protección; +1.200 participantes y 150+ iniciativas de proyectos.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3938,14 +3761,14 @@
           <t>https://participa.mpudahuel.cl/</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>DUDA</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Pendiente de validación: confirmar si hay IA en el proceso.</t>
+          <t>Presupuesto participativo real, pero solo se confirma que la plataforma (Go Vocal) tiene el módulo de IA/NLP de fábrica; no hay traza de que Pudahuel lo activara sobre los aportes, sin evidencia). Sin uso de IA verificado.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -3958,7 +3781,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Análisis de las audiencias públicas dentro de los mecanismos de participación ciudadana en el proceso constitucional</t>
+          <t>Análisis de las audiencias públicas dentro de los mecanismos de participación ciudadana en el proceso constitucional.</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3973,7 +3796,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Aplica a los dos casos homónimos (autoconvocados y audiencias)</t>
+          <t>Aplica a los dos casos homónimos (autoconvocados y audiencias).</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -3986,7 +3809,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Plataforma digital de participación ciudadana del Proceso Constitucional chileno 2023, gestionada por el centro tecnológico UCampus de la Facultad de Ciencias Físicas y Matemáticas (FCFM) de la Universidad de Chile.</t>
+          <t>Plataforma digital de participación ciudadana del Proceso Constitucional chileno 2023, gestionada por el centro tecnológico UCampus de la Facultad de Ciencias Físicas y Matemáticas (fcfm) de la Universidad de Chile. El proceso participativo (Mes de la Participación, 7 de junio al 7 de julio de 2023) contempló cuatro mecanismos -Audiencias Públicas, Iniciativa Popular de Norma, Diálogos Ciudadanos y Consulta Ciudadana- bajo la coordinación de la Secretaría Ejecutiva de Participación Ciudadana, entidad técnica interinstitucional conformada por la Universidad de Chile y la Pontificia Universidad Católica (Art. 153 de la Constitución). De esos cuatro mecanismos, la plataforma UCampus se encargó de dos: Audiencias Públicas e Iniciativa Popular de Norma. La función de UCampus fue articular tecnológicamente la recepción y gestión de los aportes (permitir solicitar audiencias, revisar artículos, proponer enmiendas y reunir las 10.000 firmas con ClaveÚnica), participando alrededor de 280 mil personas. La sistematización analítica de los aportes la realizó la Secretaría de Participación mediante una sistematización cualitativa encabezada por académicos y profesionales de derecho constitucional y ciencias sociales. No se halló evidencia de que UCampus aplicara inteligencia artificial / NLP sobre el contenido de los aportes ciudadanos.</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -4001,7 +3824,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>MANTENER EXCLUIDO. Existe un proceso participativo ELEGIBLE (Proceso Constitucional 2023, mecanismos de participación ciudadana con ~280 mil personas, convocado por el Estado de Chile), y UCampus (Uni</t>
+          <t>Existe un proceso participativo elegible (Proceso Constitucional 2023, mecanismos de participación ciudadana con ~280 mil personas, convocado por el Estado de Chile), y UCampus (Universidad de Chile) fue el operador técnico de dos de los cuatro mecanismos (Audiencias Públicas e Iniciativa Popular de Norma). Sin embargo, no se halló evidencia de que la plataforma UCampus aplicara IA sobre el contenido de los aportes ciudadanos (clasificar/analizar/agrupar/sintetizar). Las fuentes describen a UCampus en funciones de recepción y gestión (recibir solicitudes de audiencia, revisar artículos, proponer enmiendas, recolectar firmas con ClaveÚnica), y la sistematización analítica de los aportes la realizó la Secretaría de Participación mediante una sistematización cualitativa encabezada por académicos de derecho constitucional y ciencias sociales -no mediante NLP/IA-. Las herramientas de IA visibles en el proceso 2023 (Constitucion.AI, Discolab, ChatBot Constitucional) operaron sobre el texto de la propuesta para comprensión ciudadana, no sobre los aportes, y son proyectos independientes sin vínculo con UCampus. Por tanto, a diferencia de los cabildos 2016 (donde sí hubo análisis NLP de aportes), no se confirma IA sobre el contenido de los aportes en la plataforma UCampus 2023. Se mantiene excluido (entra=no); las URLs oficiales clave (uchile.cl, ingenieria.uchile.cl, informe oficial de la Secretaría en pdf) devolvieron http 403 y quedan en gaps para verificación manual.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -4014,7 +3837,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Senador Virtual (desde 2003; relanzado en 2020 como 'Congreso Virtual' con apoyo del BID), plataforma digital del Congreso de Chile (Senado y, desde 2020, Camara de Diputadas y Diputados) en la que la ciudadania conoce proyecto…</t>
+          <t>Senador Virtual (desde 2003; relanzado en 2020 como 'Congreso Virtual' con apoyo del BID), plataforma digital del Congreso de Chile (Senado y, desde 2020, Camara de Diputadas y Diputados) en la que la ciudadania conoce proyectos de ley en tramitacion, vota a favor/en contra y deja comentarios/opiniones antes de la votacion parlamentaria. Sobre ese proceso, el GobLab UAI (Escuela de Gobierno, Universidad Adolfo Ibanez) en alianza con la Universidad de Harvard y mediante convenio con el Senado desarrollo el proyecto de investigacion aplicada 'CrowdLaw', que estudia 15-16 anios de participacion ciudadana en la plataforma. El reto declarado del proyecto es el procesamiento de la gran cantidad de informacion recogida; la investigacion usa una metodologia mixta (analisis estadistico, entrevistas, etnografia digital) y entrega recomendaciones (entre ellas, 'anadir una metodologia confiable para procesar el aporte ciudadano', es decir, algo aun no desplegado). Por separado, el imfd (Instituto Milenio Fundamentos de los Datos) desarrolla NLP aplicado a leyes mediante la plataforma 'Vincula', orientada a conectar a academicos/investigadores con el Congreso (vincular temas de interes con expertos), no a sistematizar los aportes ciudadanos de Senador Virtual.</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -4029,7 +3852,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2a PASADA (resuelve DUDA -&gt; NO). La plataforma Senador Virtual / Congreso Virtual es un proceso participativo digital del Congreso de Chile (gobierno nacional) plenamente activo y consolidado (&gt;16 ani</t>
+          <t>(resuelve duda -&gt; no). La plataforma Senador Virtual / Congreso Virtual es un proceso participativo digital del Congreso de Chile (gobierno nacional) plenamente activo y consolidado (&gt;16 anios, &gt;130.000 participantes), pero la plataforma en si no usa IA sobre el contenido de los aportes y por tanto no basta. El componente con IA/NLP es el proyecto CrowdLaw del GobLab UAI (+ Harvard), que la evidencia describe consistentemente como investigacion academica de metodologia mixta (analisis estadistico, entrevistas, etnografia digital) aplicada retrospectivamente a 15-16 anios de datos, cuyo producto son recomendaciones de diseno; el propio articulo '16 years of CrowdLaw' indica que, para aprovechar la plataforma, hay que 'anadir una metodologia confiable para procesar el aporte ciudadano' (una capacidad aun no implementada), no que exista una herramienta de NLP en produccion. La 'senial imfd + NLP' del caso se refiere a un producto distinto (plataforma 'Vincula' del imfd: NLP para vincular temas de interes con academicos/expertos y conectarlos con el Congreso), que no procesa los aportes ciudadanos de Senador Virtual. La actualizacion BID (2018-2020) solo anadio 'analisis de datos' y 'reporte con visualizaciones para la comision' (analitica descriptiva). La literatura academica chilena (Guridi et al., Cornell, arXiv 2410.22937, 2024) concluye que los gobiernos 'no estan adoptando ampliamente' NLP para analizar las contribuciones ciudadanas, reforzando la no existencia de despliegue. Como el NLP/IA sobre el contenido de los aportes solo aparece como investigacion/recomendacion (no integrada al proceso) y no como despliegue en produccion, no es elegible. Convocante del proceso = gobierno nacional (Senado/Congreso); desarrollador del eventual componente IA = universidad (GobLab UAI) + academia (Harvard / imfd).</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -4042,7 +3865,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Primer Presupuesto Participativo 2024 de la Municipalidad de Viña del Mar ($200M CLP) para la reconstrucción de espacios públicos tras el megaincendio de feb-2024; vecinos (desde 14 años) proponen y votan proyectos en Achupalla…</t>
+          <t>Primer Presupuesto Participativo 2024 de la Municipalidad de Viña del Mar ($200M clp) para la reconstrucción de espacios públicos tras el megaincendio de feb-2024; vecinos (desde 14 años) proponen y votan proyectos en Achupallas, Reñaca Alto, Viña Oriente y Miraflores.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -4050,14 +3873,14 @@
           <t>https://vinadecide.cl/pages/presupuestoparticipativo</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>DUDA</t>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Pendiente de validación: confirmar si hay IA en el proceso.</t>
+          <t>Presupuesto participativo real sobre plataforma Go Vocal, pero no se encontró en el informe ejecutivo ninguna traza de uso de IA sobre los aportes, sin evidencia). Sin uso de IA verificado.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -4078,11 +3901,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4138,7 +3961,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Tiene módulos de participación (aportes al Plan de Desarrollo de Bogotá).</t>
+        </is>
+      </c>
       <c r="F2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4149,7 +3976,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Iniciativa del Laboratorio de Aceleración del PNUD Colombia que, en el contexto del paro nacional de 2021, usó la plataforma de IA Citibeats para monitorear y agrupar en tiempo real las opiniones y propuestas de la juventud col…</t>
+          <t>Iniciativa del Laboratorio de Aceleración del PNUD Colombia que, en el contexto del paro nacional de 2021, usó la plataforma de IA Citibeats para monitorear y agrupar en tiempo real las opiniones y propuestas de la juventud colombiana sobre la coyuntura del país, con el fin de 'mejorar la deliberación pública'. La IA filtra y clasifica contenido de fuentes abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video). En paralelo, el PNUD y aliados como El Avispero generaron espacios presenciales para contrastar lo dicho en las conversaciones en línea; no hay evidencia de que Citibeats procesara los aportes de un proceso participativo formal convocado (consulta, cabildo o deliberación con inputs estructurados), sino principalmente social listening de medios digitales.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -4173,7 +4000,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -4192,17 +4019,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Colombia</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://tenemosquehablarcolombia.co/</t>
+          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -4210,51 +4037,51 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Un LLM (DeepSeek) resume, organiza y construye consensos sobre el contenido de los aportes en un proceso participativo real (cabildo Zenú). Procesa el contenido.</t>
+        </is>
+      </c>
       <c r="F5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Asamblea ciudadana deliberativa, itinerante, integrada por grupos cambiantes de ciudadanos seleccionados por sorteo (muestreo estratificado) que representan las 20 localidades de Bogotá, con paridad de género y diversidad.</t>
+          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, NO se encontro evidencia</t>
-        </is>
-      </c>
+          <t>https://tenemosquehablarcolombia.co/</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
+          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Proceso participativo de formulación del Plan de Ordenamiento Departamental (POD) 2025-2050 del departamento del Atlántico (Colombia), liderado por la Gobernación del Atlántico (Secretaría de Planeación).</t>
+          <t>Asamblea ciudadana deliberativa, itinerante, integrada por grupos cambiantes de ciudadanos seleccionados por sorteo (muestreo estratificado) que representan las 20 localidades de Bogotá, con paridad de género y diversidad. Funciona de forma espiral: cada capitulo incorpora resultados y aprendizajes de los anteriores. Convocada por el Concejo de Bogota a traves de DemoLab (Laboratorio de Concejo Abierto). Ediciones en 2020, 2021 y 2023. Los participantes reciben formacion previa, deliberan en comisiones tematicas y entregan recomendaciones al Concejo.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
+          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -4264,7 +4091,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>NO ELEGIBLE. Dentro de un proceso participativo real (POD con mesas/talleres subregionales), la IA (plataforma LITA / base de datos con IA) cumple funciones de ALMACENAMIENTO, PROCESAMIENTO y ESTRUCTU</t>
+          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, no se encontro evidencia de uso de inteligencia artificial sobre el contenido de los aportes ciudadanos dentro del proceso participativo. La metodologia describe 'instrumentos que facilitan la sistematizacion' como innovacion metodologica/manual, sin mencion de IA, PLN ni analisis automatizado de propuestas. Las referencias a IA halladas pertenecen a iniciativas separadas: un estudio academico de 'Factibilidad de inteligencia artificial para la participacion ciudadana en la planificacion urbana de Bogota: caso del POT', que es investigacion de aceptacion/factibilidad de una herramienta propuesta, no desplegada en la Asamblea; politicas distritales de uso de IA en entidades publicas. Se mantiene la exclusion de 2025 ('No se encontro informacion sobre el uso de la IA en la implementacion de los Mini Publics'). Decision: (entra=no).</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
@@ -4272,17 +4099,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Chatbot ALBA</t>
+          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Asistente virtual de la Alcaldía de Barranquilla que facilita información sobre trámites y servicios.</t>
+          <t>Proceso participativo de formulación del Plan de Ordenamiento Departamental (pod) 2025-2050 del departamento del Atlántico (Colombia), liderado por la Gobernación del Atlántico (Secretaría de Planeación). Incluye instalación de un Comité de Coordinación Interinstitucional (20 enero 2026), Comisión Regional de Ordenamiento Territorial, mesas/talleres subregionales de co-creación en las cinco subregiones (Metropolitana, Centro, Sur, Oriental, Costera) con ~500 asistentes (diputados, alcaldes, consejos comunitarios, comunidades étnicas, gremios, academia, entidades nacionales). Como soporte tecnológico se usa la plataforma lita (Laboratorio de Innovación Territorial Atlántico), 'habilitada por IA', donde se almacena, procesa y construye la información que alimenta el documento pod, y una herramienta/base de datos con IA que permite a los municipios cruzar datos técnicos para actualizar sus planes de ordenamiento y estructurar proyectos; los resultados de los talleres se recopilan en un visor interactivo con 110 proyectos estratégicos.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://barranquilla.gov.co/chatbot</t>
+          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -4292,7 +4119,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>No elegible. Dentro de un proceso participativo real (pod con mesas/talleres subregionales), la IA (plataforma lita / base de datos con IA) cumple funciones de almacenamiento, procesamiento y estructuración de información técnica territorial y cruce de datos técnicos/geoespaciales de punta para actualizar planes de ordenamiento y estructurar proyectos. no hay evidencia en ninguna fuente de que la IA procese el contenido/texto de los aportes ciudadanos (clasificar, agrupar, resumir o analizar sentimiento de lo aportado en las mesas). Los resultados de los talleres se compilan en un 'visor interactivo', pero no se atribuye a la IA el análisis del texto de los aportes. Esto encaja exactamente en la exclusión del criterio: 'no si la IA (plataforma lita) solo cruza datos geoespaciales/técnicos o almacena/estructura info sin analizar el texto de los aportes'. Por tanto: entra=no. Reevaluar si futuras fuentes documentan que lita sistematiza/clasifica/resume el texto de los aportes ciudadanos.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -4300,17 +4127,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Chatbot Rama Judicial</t>
+          <t>Chatbot ALBA</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Este chatbot es un software que emplea IA para mantener conversaciones en tiempo real mediante texto con los usuarios.</t>
+          <t>Asistente virtual de la Alcaldía de Barranquilla que facilita información sobre trámites y servicios.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
+          <t>https://barranquilla.gov.co/chatbot</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -4320,7 +4147,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
@@ -4328,17 +4155,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Chatbot Rebecca</t>
+          <t>Chatbot Rama Judicial</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Rebeca es un Chatbot diseñado para mejorar la interacción entre la ciudadanía y RenoBo, proporcionando respuestas automáticas e inteligentes sobre servicios, trámites y proyectos de la entidad.</t>
+          <t>Este chatbot es un software que emplea IA para mantener conversaciones en tiempo real mediante texto con los usuarios. Está diseñado para proporcionar información de primer nivel relacionada con los servicios que ofrece la Rama Judicial, incluyendo detalles de contacto a nivel nacional de direcciones y consejos seccionales. Además, puede redirigir solicitudes al interior de la Rama Judicial y a otras entidades pertinentes.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
+          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4348,7 +4175,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -4356,17 +4183,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+          <t>Chatbot Rebecca</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Diálogos Regionales Vinculantes (DRV) convocados por el Gobierno Nacional (Presidencia + DNP) para construir las bases del Plan Nacional de Desarrollo 2022-2026 'Colombia, Potencia Mundial de la Vida'.</t>
+          <t>Rebeca es un Chatbot diseñado para mejorar la interacción entre la ciudadanía y RenoBo, proporcionando respuestas automáticas e inteligentes sobre servicios, trámites y proyectos de la entidad. Al estar disponible las 24 horas del día, y al utilizar procesamiento de lenguaje natural para comprender y responder de manera conversacional, Rebeca facilita que los ciudadanos accedan a información relevante de manera eficiente y personalizada.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://dialogosregionales.dnp.gov.co/</t>
+          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -4376,7 +4203,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido (verificado). Decisión del equipo.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -4384,17 +4211,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>El Departamento Administrativo para la Prosperidad Social (DPS) implementó un sistema de Inteligencia Artificial para descongestionar las solicitudes diarias del programa Ingreso Solidario, que recibía más de 10.000 correos cad…</t>
+          <t>Diálogos Regionales Vinculantes (drv) convocados por el Gobierno Nacional (Presidencia + DNP) para construir las bases del Plan Nacional de Desarrollo 2022-2026 'Colombia, Potencia Mundial de la Vida'. 51 diálogos regionales, ~250.000 participantes, 2.115 mesas de diálogo, 89.788 propuestas ciudadanas recolectadas y sistematizadas.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
+          <t>https://dialogosregionales.dnp.gov.co/</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -4404,7 +4231,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
+          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -4412,27 +4239,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
+          <t>El Departamento Administrativo para la Prosperidad Social (DPS) implementó un sistema de Inteligencia Artificial para descongestionar las solicitudes diarias del programa Ingreso Solidario, que recibía más de 10.000 correos cada día. Empleando herramientas de QnA Maker para la clasificación semántica de consultas y Azure Logic Apps para extracción de metadatos (remitente, asunto, adjuntos y contenido), el proyecto redujo en un 50 % el tiempo dedicado por los funcionarios de Participación Ciudadana, transformó un backlog de tres meses de correos en solo dos semanas y pasó de respuestas en dos meses a respuestas en cuestión de minutos.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>DUDA</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Pendiente de validación: confirmar si hay IA en el proceso.</t>
+          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -4445,7 +4272,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>El proceso participativo REAL de referencia es la formulación/revisión del Plan de Ordenamiento Territorial (POT) de Bogotá, cuyo convocante sería la Secretaría Distrital de Planeación / Concejo de Bogotá (gobierno local).</t>
+          <t>El proceso participativo real de referencia es la formulación/revisión del Plan de Ordenamiento Territorial (POT) de Bogotá, cuyo convocante sería la Secretaría Distrital de Planeación / Concejo de Bogotá (gobierno local). sin embargo, el caso documentado no es un despliegue institucional dentro de ese proceso: es un artículo académico ('Factibilidad de inteligencia artificial para la participación ciudadana en la planificación urbana de Bogotá: caso del POT') de una investigación aplicada de enfoque mixto y alcance exploratorio que mide la factibilidad/aceptación de una herramienta de IA propuesta para fomentar la participación ciudadana en el POT. La 'participación' del estudio consistió en encuestar a 395 ciudadanos y entrevistar a expertos urbanistas para evaluar la aceptación de la propuesta, no en aplicar IA al contenido de aportes ciudadanos de un proceso participativo institucional en curso. La (búsqueda dirigida) no halló ningún despliegue institucional de IA sobre aportes ciudadanos reales del POT; los despliegues reales de IA hallados en la SDP (ISIDataInsights / 'Inteligencia 360°' / reto 'Datos con Historia' / Chatico) corresponden al Plan Distrital de desarrollo 'Bogotá Camina Segura' 2024-2028, no al POT, y son casos distintos.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4460,7 +4287,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCUL</t>
+          <t>El criterio de elegibilidad exige que dentro de un proceso participativo se despliegue IA real (institucional) sobre el contenido de los aportes ciudadanos. El caso documentado es un artículo académico (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revista Control Visible de la Auditoría General) de una 'investigación aplicada de enfoque mixto y alcance exploratorio dada la innovación de la propuesta', cuyo objetivo es 'identificar la factibilidad de aceptación de una herramienta de inteligencia artificial' para la participación en el POT. Es decir, propone/evalúa una herramienta de IA y mide su aceptación encuestando a 395 ciudadanos y entrevistando a expertos urbanistas; no despliega IA sobre aportes reales de un proceso participativo institucional en curso. La (búsqueda dirigida: 8 búsquedas web + 4 intentos de fetch) no halló ningún despliegue institucional de IA sobre aportes ciudadanos reales del POT por parte de la Secretaría Distrital de Planeación, el Concejo de Bogotá o la Auditoría. Los despliegues reales de IA de la SDP que sí aparecen (ISIDataInsights / 'Inteligencia 360°' / reto 'Datos con Historia', oct-nov 2024; Chatico vía WhatsApp) están explícitamente ligados al Plan Distrital de desarrollo 'Bogotá Camina Segura' 2024-2028 (la fuente indica que 'Datos con Historia' fue 'el primero de cinco' retos de la estrategia '5 en Innovación' del Plan de Desarrollo), no al POT, y constituyen casos distintos. Por ello el veredicto pasa de duda a no: se trata de un artículo/propuesta (estudio de aceptación), no de un caso desplegado., no IA aplicada a aportes; no hay IA en operación sobre el proceso);; nivel_consolidacion=0; tipo_convocante=universidad (autor del estudio).</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -4473,7 +4300,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Reto de Ciudad No.</t>
+          <t>Reto de Ciudad No. 1 'Datos con Historia': convocatoria de innovación abierta de la Oficina Laboratorio de Ciudad de la Secretaría Distrital de Planeación (SDP) de Bogotá y la Corporación Maloka (primero de los cinco retos de la estrategia '5 en Innovación' del Plan de Desarrollo 'Bogotá Camina Segura' 2024-2028), realizada entre el 30 de octubre y el 15 de noviembre de 2024. El reto buscaba automatizar la recolección, análisis y categorización de información cualitativa gestionada por la SDP (incluidos los aportes ciudadanos y la información generada por entidades distritales sobre planes y políticas en ejecución) mediante desarrollo tecnológico, para integrarla en la toma de decisiones de planeación urbana. La solución ganadora, ISIDataInsights (de Inversiones Gutiérrez García y Cía – igg), procesa documentos, valida su consistencia y aplica modelos de IA para identificar patrones clave. nota: el caso es la herramienta ganadora del concurso, en fase de integración a los sistemas del Distrito; tras una de investigación dirigida (jun-2026) no se halló evidencia de su aplicación operativa al contenido de los aportes de un proceso participativo concreto (pdd, POT, consulta, presupuesto participativo, etc.).</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4488,7 +4315,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de </t>
+          <t>Duda con inclinación no (reafirmada en con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el contenido de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, aplicar modelos de IA para identificar patrones clave, analizar datos cualitativos), lo que en principio encajaría con el criterio de IA sobre el contenido de los aportes dentro de un marco de planeación. Por otro lado —y de forma determinante tras 2ª (jun-2026) y 3ª (jul-2026) pasadas de investigación— el caso documentado es una herramienta ganadora de un concurso de innovación abierta (Reto de Ciudad 'Datos con Historia', SDP+Maloka, oct-nov 2024) que, en todas las fuentes disponibles, sigue descrita en fase prospectiva: 'entra en una tercera etapa, donde será integrada a los sistemas de información del Distrito' / 'la solución se implementará para que se incorpore a los sistemas donde la ciudad recoge información'. no existe evidencia de aplicación operativa real al contenido de los aportes de un proceso participativo concreto (consulta, cabildo, presupuesto participativo, construcción del pdd 2024-2028, POT, etc.). La amplió los canales más allá de la SDP: (i) la empresa desarrolladora igg no muestra la herramienta como producto con clientes/despliegues; su único rastro público con ISIDataInsights es el post 'Ganamos' de LinkedIn (~dic 2024) sobre ganar el reto, sin publicación posterior de despliegue; (ii) no hay contrato en SECOP/datos.gov.co que vincule a igg con la SDP para implementación; (iii) no hay despliegues en otras ciudades de latam; (iv) el texto de Maloka/SDP sobre 'metodologías ágiles', 'sesiones de prueba y validación' y 'capacidades instaladas' describe el desarrollo/configuración de la herramienta, no el análisis de aportes reales; (v) las demás iniciativas de IA+participación en Bogotá (POT con ~20 mil aportes, estudio académico de factibilidad de IA para el POT en revista Control Visible, Ecosistema de IA Urbana de la Agencia Atenea, agente Chatico) son separadas y ninguna reporta usar ISIDataInsights sobre aportes. Conforme a la regla de elegibilidad ('herramienta ganadora de concurso pero aún sin aplicación a un proceso participativo concreto duda/no'), el balance se inclina a R por ausencia de despliegue sobre aportes ciudadanos reales; se mantiene la etiqueta por la naturaleza negativa de la evidencia (ausencia de reportes, no prueba positiva de no-uso) y por el ajuste exacto de la función prevista al criterio. Nivel de consolidación bajo (1, anuncio). advertencia importante: existe una iniciativa distinta y separada de la SDP donde la ciudadanía participa en la construcción del Plan de Desarrollo mediante IA a través del agente virtual 'Chatico' (WhatsApp); esa no es ISIDataInsights y no debe conflarse con este caso.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -4501,7 +4328,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Mini-público / diálogo social impulsado por la Procuraduría General de la Nación de Colombia (estrategia de 'Diálogo Social' / 'Diálogo para construir consensos' / 'Escuelas de Diálogo de la PGN'), con facilitación metodológica…</t>
+          <t>Mini-público / diálogo social impulsado por la Procuraduría General de la Nación de Colombia (estrategia de 'Diálogo Social' / 'Diálogo para construir consensos' / 'Escuelas de Diálogo de la pgn'), con facilitación metodológica del laboratorio de innovación democrática ideemos. Se describe como un mecanismo y metodología de diálogo deliberativo para tejer acuerdos entre la sociedad civil, el sector privado, las instituciones públicas y la academia, basado en la confianza ciudadana en el diálogo para alcanzar la convivencia pacífica. Es un proceso participativo deliberativo elegible por su naturaleza (mini-público), pero no se encontró evidencia de que se utilice inteligencia artificial sobre el contenido de los aportes ciudadanos (sistematización, clasificación o análisis automatizado de las contribuciones).</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -4516,7 +4343,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su</t>
+          <t>Se mantiene excluido (entra=no), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es elegible por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la Nación y facilitado por ideemos), pero el criterio de inclusión exige evidencia de IA sobre el contenido de los aportes ciudadanos dentro del proceso participativo, y no se encontró ninguna. Todas las fuentes describen el diálogo social como una metodología de deliberación y construcción de acuerdos (mesas, escuelas de diálogo, espacios de investigación y diálogo), sin mención de procesamiento de lenguaje natural, machine learning, clasificación/clustering automatizado, relatoría asistida por IA ni sistematización automatizada de las contribuciones. Las referencias a IA de la Procuraduría que sí aparecen son ajenas al proceso participativo: (a) una herramienta de consulta con IA para la Guía Disciplinaria (asuntos disciplinarios, nov-2025) y (b) preparación frente a redes/algoritmos/IA y desinformación para 'proteger la democracia' (foro Semana). Ninguna procesa los aportes de los mini-públicos. No se trata de duda porque no hay indicios reales (aunque no concluyentes) de IA sobre el contenido de los aportes; simplemente hay ausencia de evidencia, igual que en 2025.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -4529,7 +4356,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Monitor de inversion publica de la Alcaldia de Santiago de Cali.</t>
+          <t>Monitor de inversion publica de la Alcaldia de Santiago de Cali. Es una plataforma digital (web y movil) de transparencia y control social construida sobre la iniciativa MapaInversiones / InvestmentMap del Banco Interamericano de Desarrollo (BID). Permite a la ciudadania consultar, filtrar y hacer seguimiento al avance de mas de 1.400 proyectos financiados con recursos publicos en las 22 comunas y 15 corregimientos de Cali (sectores salud, seguridad, infraestructura, deporte, cultura, desarrollo economico), asi como los contratos asociados. Lanzamiento oficial el 6 de marzo de 2025. Funcion central: traducir el lenguaje presupuestal complejo en datos claros para el ciudadano promedio (dashboard de datos abiertos). En su forma es una plataforma de Participacion Digital de control social, pero su nucleo es visualizacion/consulta de datos de gasto publico, no el procesamiento de aportes/quejas ciudadanas. Funcionalidades de 'reportes ciudadanos, alertas de irregularidades y envio de fotografias por la comunidad' aparecen anunciadas como evolucion futura, no como capacidad operativa actual procesada por IA.</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -4544,7 +4371,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de lo</t>
+          <t>Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, no se encontro evidencia de uso de inteligencia artificial sobre el contenido de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un monitor de inversion publica (dashboard de datos abiertos) construido sobre MapaInversiones del BID: visualiza, filtra y permite hacer seguimiento al gasto y los contratos publicos. Las menciones a IA en Cali (chatbots para consulta ciudadana, analisis predictivo para mitigacion de riesgos naturales como deslizamientos/dengue, seguridad) pertenecen a iniciativas separadas del ecosistema smart-city de la Alcaldia y se listan junto a 'Pa' que veas' solo como ejemplos de la estrategia de IA de la ciudad; el monitor aparece encuadrado unicamente en 'gestion eficiente de datos para... seguimiento a la inversion publica', no como IA aplicada a quejas. Las funcionalidades de reportes ciudadanos, alertas de irregularidades y envio de fotografias por la comunidad estan anunciadas como evolucion futura del sistema ('continuara evolucionando con nuevas funcionalidades'), no operan hoy y no hay evidencia de que vayan a ser procesadas por IA sobre su contenido. No se cumple el criterio de inclusión (IA sobre el contenido de los aportes ciudadanos dentro de un proceso participativo). Se mantiene la exclusion de 2025 ('No evidencia de uso de IA'). Decision: (entra=no).</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -4557,7 +4384,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Monitorear en tiempo real la opinión ciudadana para ajustar campañas de comunicación y responder preguntas públicas</t>
+          <t>Monitorear en tiempo real la opinión ciudadana para ajustar campañas de comunicación y responder preguntas públicas.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -4572,7 +4399,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No evidencia de uso de IA.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -4600,7 +4427,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -4613,7 +4440,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Metodología/mecanismo de Ideemos (Laboratorio de Innovación Democrática, Bogotá, Colombia) que integra 'procesamiento de datos y participación ciudadana' para resolver problemas públicos o privados bien definidos.</t>
+          <t>Metodología/mecanismo de Ideemos (Laboratorio de Innovación Democrática, Bogotá, Colombia) que integra 'procesamiento de datos y participación ciudadana' para resolver problemas públicos o privados bien definidos. Para comprender el problema combina técnicas cuantitativas y cualitativas (encuestas, entrevistas en profundidad, analítica de datos, Inteligencia Artificial, Machine Learning, revisión documental, observación participante). Para la deliberación convoca mini-públicos: asambleas ciudadanas, jurados ciudadanos y conferencias de consenso. A los participantes se les presentan 'mediciones objetivas' y escenarios de futuro y se les invita a dialogar para construir soluciones. La IA/ML aparece como técnica de diagnóstico/insumo de contexto, no como herramienta que procese, sistematice o codifique el contenido de los aportes deliberativos de la ciudadanía. El caso aplicado documentado de mini-públicos asociado a Ideemos es la Asamblea Ciudadana Itinerante del Concejo de Bogotá (vía DemoLab), donde tampoco se halló evidencia de IA aplicada al contenido de los aportes.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4628,7 +4455,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF)</t>
+          <t>El criterio de inclusión exige evidencia de IA aplicada al contenido de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su pdf) describe 'Inteligencia Artificial' y 'Machine Learning' solo como parte de un listado de técnicas cuantitativas/cualitativas para comprender el problema (al lado de encuestas, entrevistas, revisión documental, observación participante), separadas explícitamente de las técnicas de diálogo/deliberación (mini-públicos, asambleas, jurados, conferencias de consenso). El uso de IA aparece como diagnóstico/insumo de contexto que produce 'mediciones objetivas' presentadas a la gente, no como procesamiento del contenido de los aportes deliberativos. No se halló ninguna fuente que documente que la IA sistematice, codifique, agrupe o analice las intervenciones de los participantes en un mini-público concreto. En el caso aplicado real asociado a Ideemos (Asamblea Ciudadana Itinerante del Concejo de Bogotá, vía DemoLab, 3 capítulos 2020-2023) la deliberación se describe por 'método espiral' y comisiones temáticas, sin mención de IA sobre los aportes. Por tanto la 'IA' funciona como metodología/marketing de diagnóstico sin procesamiento real del contenido participativo: (coincide con el motivo de exclusión 2025: 'No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). No se eleva a duda porque la única mención de IA es genérica y de etapa de diagnóstico, sin indicio concreto de procesamiento de contenido deliberativo.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -4649,11 +4476,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4711,7 +4538,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta (verificado). Solo opinión → fuera. Decisión del equipo.</t>
+          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta . Solo opinión fuera.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
@@ -4724,7 +4551,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Sistema de monitoreo de la ejecución de los proyectos de obras públicas en tiempo real mediante inteligencia artificial, donde los ciudadanos pueden fiscalizar y levantar alertas en caso de irregularidades y corrupción en el pr…</t>
+          <t>Sistema de monitoreo de la ejecución de los proyectos de obras públicas en tiempo real mediante inteligencia artificial, donde los ciudadanos pueden fiscalizar y levantar alertas en caso de irregularidades y corrupción en el proyecto.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -4760,11 +4587,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4807,7 +4634,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (CEN).</t>
+          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (cen). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema xiscop y luego procesadas en el sistema GEMA-cen, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). xiscop (uci) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -4822,7 +4649,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de pr</t>
+          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el contenido de los aportes ciudadanos: el sistema GEMA-cen (basado en GEMA de Datys) hacía 'análisis inteligente de los expedientes' para recuperar, comparar y agrupar propuestas similares y determinar 'propuestas típicas' por párrafo/categoría (5.237 propuestas típicas), es decir recolectar/clasificar/agrupar/sintetizar el contenido de los aportes, no apoyo logístico. La ficha técnica oficial de GEMA (Datys) lo describe como herramienta de recuperación y clasificación de información en grandes volúmenes de archivos, con OCR, agrupamiento de documentos comunes y resumen automático, lo que corresponde a NLP/minería de texto/recuperación de información (IA sobre contenido), no a mero conteo o lógica de reglas determinista. Convocante = gobierno nacional (Consejo Electoral Nacional / Asamblea Nacional, Estado cubano). Por ello entra. Se mantiene clasificado en bloque '1-dudoso' y con alerta porque las fuentes no precisan si el agrupamiento usa ML/embeddings semánticos o similitud clásica de recuperación de información; en cualquiera de los dos casos sigue siendo procesamiento de texto sobre el contenido, por lo que se resuelve como si (no duda) con confianza media-alta.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
@@ -4843,11 +4670,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4890,7 +4717,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Sistema de interacción ciudadana basado en inteligencia artificial, diseñado para recopilar datos representativos que permitan el entrenamiento avanzado de IA en la prestación de servicios públicos.</t>
+          <t>Sistema de interacción ciudadana basado en inteligencia artificial, diseñado para recopilar datos representativos que permitan el entrenamiento avanzado de IA en la prestación de servicios públicos. A través de ventanillas ubicadas en puntos estratégicos de alto tránsito, ofrece asistencia, información y recomendaciones personalizadas, fomentando la participación activa de la ciudadanía en el diseño y desarrollo de un sistema de Gobierno Inteligente.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -4905,7 +4732,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
+          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
@@ -4933,7 +4760,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
@@ -4946,7 +4773,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Plataforma de IA conversacional de texto y voz para tramitar servicios públicos y anticipar necesidades ciudadanas, parte de la Estrategia Nacional de Inteligencia Artificial (ENIA)</t>
+          <t>Plataforma de IA conversacional de texto y voz para tramitar servicios públicos y anticipar necesidades ciudadanas, parte de la Estrategia Nacional de Inteligencia Artificial (enia).</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -4961,7 +4788,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>

--- a/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
+++ b/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1 casos  (SÍ 0 · DUDA 0 · NO 1)</t>
+          <t>1 casos  (SÍ 1 · DUDA 0 · NO 0)</t>
         </is>
       </c>
     </row>
@@ -4642,16 +4642,12 @@
           <t>http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el contenido de los aportes ciudadanos: el sistema GEMA-cen (basado en GEMA de Datys) hacía 'análisis inteligente de los expedientes' para recuperar, comparar y agrupar propuestas similares y determinar 'propuestas típicas' por párrafo/categoría (5.237 propuestas típicas), es decir recolectar/clasificar/agrupar/sintetizar el contenido de los aportes, no apoyo logístico. La ficha técnica oficial de GEMA (Datys) lo describe como herramienta de recuperación y clasificación de información en grandes volúmenes de archivos, con OCR, agrupamiento de documentos comunes y resumen automático, lo que corresponde a NLP/minería de texto/recuperación de información (IA sobre contenido), no a mero conteo o lógica de reglas determinista. Convocante = gobierno nacional (Consejo Electoral Nacional / Asamblea Nacional, Estado cubano). Por ello entra. Se mantiene clasificado en bloque '1-dudoso' y con alerta porque las fuentes no precisan si el agrupamiento usa ML/embeddings semánticos o similitud clásica de recuperación de información; en cualquiera de los dos casos sigue siendo procesamiento de texto sobre el contenido, por lo que se resuelve como si (no duda) con confianza media-alta.</t>
-        </is>
-      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
+++ b/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Atención automatizada mediante procesamiento de lenguaje natural, análisis de datos y algoritmos de inteligencia artificial para responder consultas ciudadanas sobre más de 400 temas de interés.</t>
+          <t>Agente virtual de Bogotá (Secretaría General) con módulos de participación además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa ; atiende por WhatsApp/Telegram/webchat.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">

--- a/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
+++ b/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>23 casos  (SÍ 9 · DUDA 0 · NO 14)</t>
+          <t>23 casos  (SÍ 8 · DUDA 0 · NO 15)</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>19 casos  (SÍ 5 · DUDA 0 · NO 14)</t>
+          <t>19 casos  (SÍ 4 · DUDA 0 · NO 15)</t>
         </is>
       </c>
     </row>
@@ -2841,17 +2841,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
+          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Investigación académica (Co:Lab USP / Cátedra Brasil-Alemania, getip) sobre el uso de IA generativa para apoyar a la ciudadanía a redactar y estructurar propuestas en procesos de participación, tomando como referencia el orçamento participativo de São Paulo. Descrito como 'pesquisas em andamento' / proyecto de investigación-prototipo, no como una herramienta oficial desplegada en el proceso real (que opera vía la plataforma Participe+/Participe Mais de la Prefeitura, sin IA generativa confirmada).</t>
+          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/</t>
+          <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2865,17 +2865,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
+          <t>Plan Plurianual de la ciudad de Natal</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
+          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2889,17 +2889,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
+          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
+          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
+          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
+          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+          <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2937,17 +2937,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
+          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
+          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2955,33 +2955,37 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Cuenta junto con su par (no se suma como iniciativa aparte).</t>
+        </is>
+      </c>
       <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
+          <t>BP-Classificador de Propostas (indexação/classificação automática ML de propuestas de Brasil Participativo) - Residência TIC BRISA / UnB-FGA / LAPPIS</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
+          <t>Brasil Participativo es la plataforma digital de participación social del Gobierno Federal de Brasil, construida sobre el software libre Decidim y lanzada en 2023 por la Secretaria Nacional de Participação Social (Secretaria-Geral da Presidência da República). El repositorio bp-Classificador-de-Propostas (Residência TIC brisa, en alianza con UnB-Gama/fga y lappis) es un componente de IA que hace 'Indexação Automática com ML das propostas publicadas no Brasil Participativo': un modelo de clasificación (scikit-learn/nltk) reentrenado a diario con Apache Airflow sobre los datos de la plataforma, expuesto como servicio Python + una gema Ruby ('proposal-classifier') para integrarse a plataformas web 'afim de ser integrado a plataforma do Brasil Participativo'. Este componente es el mismo esfuerzo de indexación/clasificación de propuestas ya documentado en la ficha br-brasil-participativo-clustering-semantic (que cita este mismo repositorio y los papers arXiv 2509.21292 -clustering semántico BERTopic+LLM- y 2511.01545 -'From Pre-labeling to Production', lecciones de ingeniería del pipeline ML en el sector público- como su evidencia).</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>SÍ</t>
+          <t>https://github.com/ResidenciaTICBrisa/BP-Classificador-de-Propostas</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Cuenta junto con su par (no se suma como iniciativa aparte).</t>
+          <t>Por doble conteo. Este candidato (bp-Classificador-de-Propostas, Residência TIC brisa / UnB-fga / lappis) es el mismo caso ya contabilizado en la ficha br-brasil-participativo-clustering-semantic, no un caso distinto. Prueba directa: (a) esa ficha ya cita este mismo repositorio (https://github.com/ResidenciaTICBrisa/bp-Classificador-de-Propostas) como una de sus fuentes (estado ok) y lo describe explícitamente; (b) su alerta de alcance reconoce 'al menos dos artefactos de IA relacionados pero distintos: (a) el pipeline de clustering semántico BERTopic+LLM (papers) y (b) el clasificador supervisado ML bp-Classificador-de-Propostas (scikit-learn/Airflow, GitHub). Ambos operan sobre las propuestas de Brasil Participativo y comparten autores/laboratorio; se documentan juntos en esta ficha por pertenecer al mismo esfuerzo de indexación/clasificación de aportes'; (c) los papers que sustentan la ficha contada (arXiv 2509.21292 'Semantic Clustering' y 2511.01545 'From Pre-labeling to Production') son la producción académica de este mismo equipo y describen la evolución de este mismo clasificador. Es, por tanto, un componente/duplicado del caso Brasil Participativo ya contado, no un despliegue independiente en un proceso participativo distinto. Adicionalmente, el criterio de producción tampoco se cumple: la integración a la plataforma oficial se describe como intención ('afim de ser integrado a plataforma do Brasil Participativo'), no como despliegue confirmado; no se halló fuente gubernamental que confirme el clasificador operando en producción (el relanzamiento oficial de 15/08/2025 no menciona clasificación automática por IA). Se distingue del pipeline BERTopic (arXiv 2509.21292) solo como su arm de 'clasificación supervisada', pero ambos pertenecen al mismo caso ya listado. Veredicto: no (doble conteo con br-brasil-participativo-clustering-semantic).</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -2989,17 +2993,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>BP-Classificador de Propostas (indexação/classificação automática ML de propuestas de Brasil Participativo) - Residência TIC BRISA / UnB-FGA / LAPPIS</t>
+          <t>Busca por voz</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Brasil Participativo es la plataforma digital de participación social del Gobierno Federal de Brasil, construida sobre el software libre Decidim y lanzada en 2023 por la Secretaria Nacional de Participação Social (Secretaria-Geral da Presidência da República). El repositorio bp-Classificador-de-Propostas (Residência TIC brisa, en alianza con UnB-Gama/fga y lappis) es un componente de IA que hace 'Indexação Automática com ML das propostas publicadas no Brasil Participativo': un modelo de clasificación (scikit-learn/nltk) reentrenado a diario con Apache Airflow sobre los datos de la plataforma, expuesto como servicio Python + una gema Ruby ('proposal-classifier') para integrarse a plataformas web 'afim de ser integrado a plataforma do Brasil Participativo'. Este componente es el mismo esfuerzo de indexación/clasificación de propuestas ya documentado en la ficha br-brasil-participativo-clustering-semantic (que cita este mismo repositorio y los papers arXiv 2509.21292 -clustering semántico BERTopic+LLM- y 2511.01545 -'From Pre-labeling to Production', lecciones de ingeniería del pipeline ML en el sector público- como su evidencia).</t>
+          <t>El Gobierno de Brasil ha lanzado una nueva funcionalidad de búsqueda por voz en el portal gov.br, permitiendo a los usuarios acceder a más de 4.300 servicios digitales mediante comandos de voz. Esta iniciativa, busca facilitar la ciudadanía digital, especialmente para personas con discapacidad visual o dificultades para escribir.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/ResidenciaTICBrisa/BP-Classificador-de-Propostas</t>
+          <t>https://www.gov.br/governodigital/pt-br/noticias/gestao-divulga-201cbusca-por-voz201d-no-gov-br-para-ampliar-inclusao-digital</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -3009,7 +3013,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Por doble conteo. Este candidato (bp-Classificador-de-Propostas, Residência TIC brisa / UnB-fga / lappis) es el mismo caso ya contabilizado en la ficha br-brasil-participativo-clustering-semantic, no un caso distinto. Prueba directa: (a) esa ficha ya cita este mismo repositorio (https://github.com/ResidenciaTICBrisa/bp-Classificador-de-Propostas) como una de sus fuentes (estado ok) y lo describe explícitamente; (b) su alerta de alcance reconoce 'al menos dos artefactos de IA relacionados pero distintos: (a) el pipeline de clustering semántico BERTopic+LLM (papers) y (b) el clasificador supervisado ML bp-Classificador-de-Propostas (scikit-learn/Airflow, GitHub). Ambos operan sobre las propuestas de Brasil Participativo y comparten autores/laboratorio; se documentan juntos en esta ficha por pertenecer al mismo esfuerzo de indexación/clasificación de aportes'; (c) los papers que sustentan la ficha contada (arXiv 2509.21292 'Semantic Clustering' y 2511.01545 'From Pre-labeling to Production') son la producción académica de este mismo equipo y describen la evolución de este mismo clasificador. Es, por tanto, un componente/duplicado del caso Brasil Participativo ya contado, no un despliegue independiente en un proceso participativo distinto. Adicionalmente, el criterio de producción tampoco se cumple: la integración a la plataforma oficial se describe como intención ('afim de ser integrado a plataforma do Brasil Participativo'), no como despliegue confirmado; no se halló fuente gubernamental que confirme el clasificador operando en producción (el relanzamiento oficial de 15/08/2025 no menciona clasificación automática por IA). Se distingue del pipeline BERTopic (arXiv 2509.21292) solo como su arm de 'clasificación supervisada', pero ambos pertenecen al mismo caso ya listado. Veredicto: no (doble conteo con br-brasil-participativo-clustering-semantic).</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -3017,17 +3021,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Busca por voz</t>
+          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>El Gobierno de Brasil ha lanzado una nueva funcionalidad de búsqueda por voz en el portal gov.br, permitiendo a los usuarios acceder a más de 4.300 servicios digitales mediante comandos de voz. Esta iniciativa, busca facilitar la ciudadanía digital, especialmente para personas con discapacidad visual o dificultades para escribir.</t>
+          <t>Investigación académica (Co:Lab USP / Cátedra Brasil-Alemania, getip) sobre el uso de IA generativa para apoyar a la ciudadanía a redactar y estructurar propuestas en procesos de participación, tomando como referencia el orçamento participativo de São Paulo. Descrito como 'pesquisas em andamento' / proyecto de investigación-prototipo, no como una herramienta oficial desplegada en el proceso real (que opera vía la plataforma Participe+/Participe Mais de la Prefeitura, sin IA generativa confirmada).</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://www.gov.br/governodigital/pt-br/noticias/gestao-divulga-201cbusca-por-voz201d-no-gov-br-para-ampliar-inclusao-digital</t>
+          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -3037,7 +3041,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Investigación académica en curso ('pesquisas em andamento') sobre IA generativa para participación: sin despliegue con ciudadanos ni proceso propio . Estudio sin despliegue.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -3971,17 +3975,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
+          <t>ECHO – HáblameD Medellín</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Iniciativa del Laboratorio de Aceleración del PNUD Colombia que, en el contexto del paro nacional de 2021, usó la plataforma de IA Citibeats para monitorear y agrupar en tiempo real las opiniones y propuestas de la juventud colombiana sobre la coyuntura del país, con el fin de 'mejorar la deliberación pública'. La IA filtra y clasifica contenido de fuentes abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video). En paralelo, el PNUD y aliados como El Avispero generaron espacios presenciales para contrastar lo dicho en las conversaciones en línea; no hay evidencia de que Citibeats procesara los aportes de un proceso participativo formal convocado (consulta, cabildo o deliberación con inputs estructurados), sino principalmente social listening de medios digitales.</t>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia</t>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -3995,17 +3999,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial.</t>
+          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -4013,23 +4017,27 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Un LLM (DeepSeek) resume, organiza y construye consensos sobre el contenido de los aportes en un proceso participativo real (cabildo Zenú). Procesa el contenido.</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
+          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
+          <t>https://tenemosquehablarcolombia.co/</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -4037,51 +4045,51 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Un LLM (DeepSeek) resume, organiza y construye consensos sobre el contenido de los aportes en un proceso participativo real (cabildo Zenú). Procesa el contenido.</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Colombia</t>
+          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+          <t>Asamblea ciudadana deliberativa, itinerante, integrada por grupos cambiantes de ciudadanos seleccionados por sorteo (muestreo estratificado) que representan las 20 localidades de Bogotá, con paridad de género y diversidad. Funciona de forma espiral: cada capitulo incorpora resultados y aprendizajes de los anteriores. Convocada por el Concejo de Bogota a traves de DemoLab (Laboratorio de Concejo Abierto). Ediciones en 2020, 2021 y 2023. Los participantes reciben formacion previa, deliberan en comisiones tematicas y entregan recomendaciones al Concejo.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://tenemosquehablarcolombia.co/</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
+          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, no se encontro evidencia de uso de inteligencia artificial sobre el contenido de los aportes ciudadanos dentro del proceso participativo. La metodologia describe 'instrumentos que facilitan la sistematizacion' como innovacion metodologica/manual, sin mencion de IA, PLN ni analisis automatizado de propuestas. Las referencias a IA halladas pertenecen a iniciativas separadas: un estudio academico de 'Factibilidad de inteligencia artificial para la participacion ciudadana en la planificacion urbana de Bogota: caso del POT', que es investigacion de aceptacion/factibilidad de una herramienta propuesta, no desplegada en la Asamblea; politicas distritales de uso de IA en entidades publicas. Se mantiene la exclusion de 2025 ('No se encontro informacion sobre el uso de la IA en la implementacion de los Mini Publics'). Decision: (entra=no).</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
+          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Asamblea ciudadana deliberativa, itinerante, integrada por grupos cambiantes de ciudadanos seleccionados por sorteo (muestreo estratificado) que representan las 20 localidades de Bogotá, con paridad de género y diversidad. Funciona de forma espiral: cada capitulo incorpora resultados y aprendizajes de los anteriores. Convocada por el Concejo de Bogota a traves de DemoLab (Laboratorio de Concejo Abierto). Ediciones en 2020, 2021 y 2023. Los participantes reciben formacion previa, deliberan en comisiones tematicas y entregan recomendaciones al Concejo.</t>
+          <t>Proceso participativo de formulación del Plan de Ordenamiento Departamental (pod) 2025-2050 del departamento del Atlántico (Colombia), liderado por la Gobernación del Atlántico (Secretaría de Planeación). Incluye instalación de un Comité de Coordinación Interinstitucional (20 enero 2026), Comisión Regional de Ordenamiento Territorial, mesas/talleres subregionales de co-creación en las cinco subregiones (Metropolitana, Centro, Sur, Oriental, Costera) con ~500 asistentes (diputados, alcaldes, consejos comunitarios, comunidades étnicas, gremios, academia, entidades nacionales). Como soporte tecnológico se usa la plataforma lita (Laboratorio de Innovación Territorial Atlántico), 'habilitada por IA', donde se almacena, procesa y construye la información que alimenta el documento pod, y una herramienta/base de datos con IA que permite a los municipios cruzar datos técnicos para actualizar sus planes de ordenamiento y estructurar proyectos; los resultados de los talleres se recopilan en un visor interactivo con 110 proyectos estratégicos.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
+          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -4091,7 +4099,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, no se encontro evidencia de uso de inteligencia artificial sobre el contenido de los aportes ciudadanos dentro del proceso participativo. La metodologia describe 'instrumentos que facilitan la sistematizacion' como innovacion metodologica/manual, sin mencion de IA, PLN ni analisis automatizado de propuestas. Las referencias a IA halladas pertenecen a iniciativas separadas: un estudio academico de 'Factibilidad de inteligencia artificial para la participacion ciudadana en la planificacion urbana de Bogota: caso del POT', que es investigacion de aceptacion/factibilidad de una herramienta propuesta, no desplegada en la Asamblea; politicas distritales de uso de IA en entidades publicas. Se mantiene la exclusion de 2025 ('No se encontro informacion sobre el uso de la IA en la implementacion de los Mini Publics'). Decision: (entra=no).</t>
+          <t>No elegible. Dentro de un proceso participativo real (pod con mesas/talleres subregionales), la IA (plataforma lita / base de datos con IA) cumple funciones de almacenamiento, procesamiento y estructuración de información técnica territorial y cruce de datos técnicos/geoespaciales de punta para actualizar planes de ordenamiento y estructurar proyectos. no hay evidencia en ninguna fuente de que la IA procese el contenido/texto de los aportes ciudadanos (clasificar, agrupar, resumir o analizar sentimiento de lo aportado en las mesas). Los resultados de los talleres se compilan en un 'visor interactivo', pero no se atribuye a la IA el análisis del texto de los aportes. Esto encaja exactamente en la exclusión del criterio: 'no si la IA (plataforma lita) solo cruza datos geoespaciales/técnicos o almacena/estructura info sin analizar el texto de los aportes'. Por tanto: entra=no. Reevaluar si futuras fuentes documentan que lita sistematiza/clasifica/resume el texto de los aportes ciudadanos.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
@@ -4099,17 +4107,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
+          <t>Chatbot ALBA</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Proceso participativo de formulación del Plan de Ordenamiento Departamental (pod) 2025-2050 del departamento del Atlántico (Colombia), liderado por la Gobernación del Atlántico (Secretaría de Planeación). Incluye instalación de un Comité de Coordinación Interinstitucional (20 enero 2026), Comisión Regional de Ordenamiento Territorial, mesas/talleres subregionales de co-creación en las cinco subregiones (Metropolitana, Centro, Sur, Oriental, Costera) con ~500 asistentes (diputados, alcaldes, consejos comunitarios, comunidades étnicas, gremios, academia, entidades nacionales). Como soporte tecnológico se usa la plataforma lita (Laboratorio de Innovación Territorial Atlántico), 'habilitada por IA', donde se almacena, procesa y construye la información que alimenta el documento pod, y una herramienta/base de datos con IA que permite a los municipios cruzar datos técnicos para actualizar sus planes de ordenamiento y estructurar proyectos; los resultados de los talleres se recopilan en un visor interactivo con 110 proyectos estratégicos.</t>
+          <t>Asistente virtual de la Alcaldía de Barranquilla que facilita información sobre trámites y servicios.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
+          <t>https://barranquilla.gov.co/chatbot</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -4119,7 +4127,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>No elegible. Dentro de un proceso participativo real (pod con mesas/talleres subregionales), la IA (plataforma lita / base de datos con IA) cumple funciones de almacenamiento, procesamiento y estructuración de información técnica territorial y cruce de datos técnicos/geoespaciales de punta para actualizar planes de ordenamiento y estructurar proyectos. no hay evidencia en ninguna fuente de que la IA procese el contenido/texto de los aportes ciudadanos (clasificar, agrupar, resumir o analizar sentimiento de lo aportado en las mesas). Los resultados de los talleres se compilan en un 'visor interactivo', pero no se atribuye a la IA el análisis del texto de los aportes. Esto encaja exactamente en la exclusión del criterio: 'no si la IA (plataforma lita) solo cruza datos geoespaciales/técnicos o almacena/estructura info sin analizar el texto de los aportes'. Por tanto: entra=no. Reevaluar si futuras fuentes documentan que lita sistematiza/clasifica/resume el texto de los aportes ciudadanos.</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -4127,17 +4135,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Chatbot ALBA</t>
+          <t>Chatbot Rama Judicial</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Asistente virtual de la Alcaldía de Barranquilla que facilita información sobre trámites y servicios.</t>
+          <t>Este chatbot es un software que emplea IA para mantener conversaciones en tiempo real mediante texto con los usuarios. Está diseñado para proporcionar información de primer nivel relacionada con los servicios que ofrece la Rama Judicial, incluyendo detalles de contacto a nivel nacional de direcciones y consejos seccionales. Además, puede redirigir solicitudes al interior de la Rama Judicial y a otras entidades pertinentes.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://barranquilla.gov.co/chatbot</t>
+          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -4155,17 +4163,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Chatbot Rama Judicial</t>
+          <t>Chatbot Rebecca</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Este chatbot es un software que emplea IA para mantener conversaciones en tiempo real mediante texto con los usuarios. Está diseñado para proporcionar información de primer nivel relacionada con los servicios que ofrece la Rama Judicial, incluyendo detalles de contacto a nivel nacional de direcciones y consejos seccionales. Además, puede redirigir solicitudes al interior de la Rama Judicial y a otras entidades pertinentes.</t>
+          <t>Rebeca es un Chatbot diseñado para mejorar la interacción entre la ciudadanía y RenoBo, proporcionando respuestas automáticas e inteligentes sobre servicios, trámites y proyectos de la entidad. Al estar disponible las 24 horas del día, y al utilizar procesamiento de lenguaje natural para comprender y responder de manera conversacional, Rebeca facilita que los ciudadanos accedan a información relevante de manera eficiente y personalizada.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
+          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4175,7 +4183,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Atención ciudadana.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -4183,17 +4191,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Chatbot Rebecca</t>
+          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rebeca es un Chatbot diseñado para mejorar la interacción entre la ciudadanía y RenoBo, proporcionando respuestas automáticas e inteligentes sobre servicios, trámites y proyectos de la entidad. Al estar disponible las 24 horas del día, y al utilizar procesamiento de lenguaje natural para comprender y responder de manera conversacional, Rebeca facilita que los ciudadanos accedan a información relevante de manera eficiente y personalizada.</t>
+          <t>Iniciativa del Laboratorio de Aceleración del PNUD Colombia que, en el contexto del paro nacional de 2021, usó la plataforma de IA Citibeats para monitorear y agrupar en tiempo real las opiniones y propuestas de la juventud colombiana sobre la coyuntura del país, con el fin de 'mejorar la deliberación pública'. La IA filtra y clasifica contenido de fuentes abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video). En paralelo, el PNUD y aliados como El Avispero generaron espacios presenciales para contrastar lo dicho en las conversaciones en línea; no hay evidencia de que Citibeats procesara los aportes de un proceso participativo formal convocado (consulta, cabildo o deliberación con inputs estructurados), sino principalmente social listening de medios digitales.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
+          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -4203,7 +4211,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>Escucha social de redes abiertas (Twitter/Facebook) durante el paro de 2021: no hay proceso participativo convocado . Misma regla que U-Report (solo opinión).</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>

--- a/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
+++ b/data/gates/planilla_validacion_por_pais_ILIA2026.xlsx
@@ -32,7 +32,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AR - Argentina'!$A$1:$F$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BO - Bolivia'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BR - Brasil'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BR - Brasil'!$A$1:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CL - Chile'!$A$1:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CO - Colombia'!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CR - Costa Rica'!$A$1:$F$3</definedName>
@@ -666,7 +666,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>23 casos  (SÍ 8 · DUDA 0 · NO 15)</t>
+          <t>24 casos  (SÍ 9 · DUDA 0 · NO 15)</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2841,17 +2841,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
+          <t>Meta Community Forum on Generative AI — cohorte Brasil (Deliberative Polling, Stanford)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
+          <t>Foro comunitario deliberativo (Deliberative Polling®) sobre principios para los chatbots de IA generativa, realizado el 28-29 de octubre de 2023 en la Stanford Online Deliberation Platform con 1.545 participantes de muestras científicas de Brasil, Alemania, España y ee.uu. Formato: grupos pequeños de 8-12 personas (166 grupos, con grupo de control por país), panel de expertos en plenario, cuadernillo informativo (~50 págs.) y 44 preguntas de opinión pre/post. Los resultados (publicados abr-2024) incluyen hallazgos específicos de Brasil (p. ej., fuerte oposición a relaciones románticas humano-chatbot; énfasis en perspectivas locales en las fuentes de la IA). Meta declaró que los resultados 'ayudaron a dar forma a algunas de las decisiones más fundamentales' del diseño de sus productos de IA generativa.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
+          <t>https://deliberation.stanford.edu/meta-community-forum-generative-ai-results</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2865,17 +2865,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
+          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
+          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+          <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2889,17 +2889,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
+          <t>Plan Plurianual de la ciudad de Natal</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
+          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
+          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
+          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2937,17 +2937,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
+          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
+          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
+          <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2955,37 +2955,33 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Cuenta junto con su par (no se suma como iniciativa aparte).</t>
-        </is>
-      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>BP-Classificador de Propostas (indexação/classificação automática ML de propuestas de Brasil Participativo) - Residência TIC BRISA / UnB-FGA / LAPPIS</t>
+          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Brasil Participativo es la plataforma digital de participación social del Gobierno Federal de Brasil, construida sobre el software libre Decidim y lanzada en 2023 por la Secretaria Nacional de Participação Social (Secretaria-Geral da Presidência da República). El repositorio bp-Classificador-de-Propostas (Residência TIC brisa, en alianza con UnB-Gama/fga y lappis) es un componente de IA que hace 'Indexação Automática com ML das propostas publicadas no Brasil Participativo': un modelo de clasificación (scikit-learn/nltk) reentrenado a diario con Apache Airflow sobre los datos de la plataforma, expuesto como servicio Python + una gema Ruby ('proposal-classifier') para integrarse a plataformas web 'afim de ser integrado a plataforma do Brasil Participativo'. Este componente es el mismo esfuerzo de indexación/clasificación de propuestas ya documentado en la ficha br-brasil-participativo-clustering-semantic (que cita este mismo repositorio y los papers arXiv 2509.21292 -clustering semántico BERTopic+LLM- y 2511.01545 -'From Pre-labeling to Production', lecciones de ingeniería del pipeline ML en el sector público- como su evidencia).</t>
+          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/ResidenciaTICBrisa/BP-Classificador-de-Propostas</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Por doble conteo. Este candidato (bp-Classificador-de-Propostas, Residência TIC brisa / UnB-fga / lappis) es el mismo caso ya contabilizado en la ficha br-brasil-participativo-clustering-semantic, no un caso distinto. Prueba directa: (a) esa ficha ya cita este mismo repositorio (https://github.com/ResidenciaTICBrisa/bp-Classificador-de-Propostas) como una de sus fuentes (estado ok) y lo describe explícitamente; (b) su alerta de alcance reconoce 'al menos dos artefactos de IA relacionados pero distintos: (a) el pipeline de clustering semántico BERTopic+LLM (papers) y (b) el clasificador supervisado ML bp-Classificador-de-Propostas (scikit-learn/Airflow, GitHub). Ambos operan sobre las propuestas de Brasil Participativo y comparten autores/laboratorio; se documentan juntos en esta ficha por pertenecer al mismo esfuerzo de indexación/clasificación de aportes'; (c) los papers que sustentan la ficha contada (arXiv 2509.21292 'Semantic Clustering' y 2511.01545 'From Pre-labeling to Production') son la producción académica de este mismo equipo y describen la evolución de este mismo clasificador. Es, por tanto, un componente/duplicado del caso Brasil Participativo ya contado, no un despliegue independiente en un proceso participativo distinto. Adicionalmente, el criterio de producción tampoco se cumple: la integración a la plataforma oficial se describe como intención ('afim de ser integrado a plataforma do Brasil Participativo'), no como despliegue confirmado; no se halló fuente gubernamental que confirme el clasificador operando en producción (el relanzamiento oficial de 15/08/2025 no menciona clasificación automática por IA). Se distingue del pipeline BERTopic (arXiv 2509.21292) solo como su arm de 'clasificación supervisada', pero ambos pertenecen al mismo caso ya listado. Veredicto: no (doble conteo con br-brasil-participativo-clustering-semantic).</t>
+          <t>Cuenta junto con su par (no se suma como iniciativa aparte).</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -2993,17 +2989,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Busca por voz</t>
+          <t>BP-Classificador de Propostas (indexação/classificação automática ML de propuestas de Brasil Participativo) - Residência TIC BRISA / UnB-FGA / LAPPIS</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>El Gobierno de Brasil ha lanzado una nueva funcionalidad de búsqueda por voz en el portal gov.br, permitiendo a los usuarios acceder a más de 4.300 servicios digitales mediante comandos de voz. Esta iniciativa, busca facilitar la ciudadanía digital, especialmente para personas con discapacidad visual o dificultades para escribir.</t>
+          <t>Brasil Participativo es la plataforma digital de participación social del Gobierno Federal de Brasil, construida sobre el software libre Decidim y lanzada en 2023 por la Secretaria Nacional de Participação Social (Secretaria-Geral da Presidência da República). El repositorio bp-Classificador-de-Propostas (Residência TIC brisa, en alianza con UnB-Gama/fga y lappis) es un componente de IA que hace 'Indexação Automática com ML das propostas publicadas no Brasil Participativo': un modelo de clasificación (scikit-learn/nltk) reentrenado a diario con Apache Airflow sobre los datos de la plataforma, expuesto como servicio Python + una gema Ruby ('proposal-classifier') para integrarse a plataformas web 'afim de ser integrado a plataforma do Brasil Participativo'. Este componente es el mismo esfuerzo de indexación/clasificación de propuestas ya documentado en la ficha br-brasil-participativo-clustering-semantic (que cita este mismo repositorio y los papers arXiv 2509.21292 -clustering semántico BERTopic+LLM- y 2511.01545 -'From Pre-labeling to Production', lecciones de ingeniería del pipeline ML en el sector público- como su evidencia).</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://www.gov.br/governodigital/pt-br/noticias/gestao-divulga-201cbusca-por-voz201d-no-gov-br-para-ampliar-inclusao-digital</t>
+          <t>https://github.com/ResidenciaTICBrisa/BP-Classificador-de-Propostas</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -3013,7 +3009,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Por doble conteo. Este candidato (bp-Classificador-de-Propostas, Residência TIC brisa / UnB-fga / lappis) es el mismo caso ya contabilizado en la ficha br-brasil-participativo-clustering-semantic, no un caso distinto. Prueba directa: (a) esa ficha ya cita este mismo repositorio (https://github.com/ResidenciaTICBrisa/bp-Classificador-de-Propostas) como una de sus fuentes (estado ok) y lo describe explícitamente; (b) su alerta de alcance reconoce 'al menos dos artefactos de IA relacionados pero distintos: (a) el pipeline de clustering semántico BERTopic+LLM (papers) y (b) el clasificador supervisado ML bp-Classificador-de-Propostas (scikit-learn/Airflow, GitHub). Ambos operan sobre las propuestas de Brasil Participativo y comparten autores/laboratorio; se documentan juntos en esta ficha por pertenecer al mismo esfuerzo de indexación/clasificación de aportes'; (c) los papers que sustentan la ficha contada (arXiv 2509.21292 'Semantic Clustering' y 2511.01545 'From Pre-labeling to Production') son la producción académica de este mismo equipo y describen la evolución de este mismo clasificador. Es, por tanto, un componente/duplicado del caso Brasil Participativo ya contado, no un despliegue independiente en un proceso participativo distinto. Adicionalmente, el criterio de producción tampoco se cumple: la integración a la plataforma oficial se describe como intención ('afim de ser integrado a plataforma do Brasil Participativo'), no como despliegue confirmado; no se halló fuente gubernamental que confirme el clasificador operando en producción (el relanzamiento oficial de 15/08/2025 no menciona clasificación automática por IA). Se distingue del pipeline BERTopic (arXiv 2509.21292) solo como su arm de 'clasificación supervisada', pero ambos pertenecen al mismo caso ya listado. Veredicto: no (doble conteo con br-brasil-participativo-clustering-semantic).</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -3021,17 +3017,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
+          <t>Busca por voz</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Investigación académica (Co:Lab USP / Cátedra Brasil-Alemania, getip) sobre el uso de IA generativa para apoyar a la ciudadanía a redactar y estructurar propuestas en procesos de participación, tomando como referencia el orçamento participativo de São Paulo. Descrito como 'pesquisas em andamento' / proyecto de investigación-prototipo, no como una herramienta oficial desplegada en el proceso real (que opera vía la plataforma Participe+/Participe Mais de la Prefeitura, sin IA generativa confirmada).</t>
+          <t>El Gobierno de Brasil ha lanzado una nueva funcionalidad de búsqueda por voz en el portal gov.br, permitiendo a los usuarios acceder a más de 4.300 servicios digitales mediante comandos de voz. Esta iniciativa, busca facilitar la ciudadanía digital, especialmente para personas con discapacidad visual o dificultades para escribir.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/</t>
+          <t>https://www.gov.br/governodigital/pt-br/noticias/gestao-divulga-201cbusca-por-voz201d-no-gov-br-para-ampliar-inclusao-digital</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -3041,7 +3037,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Investigación académica en curso ('pesquisas em andamento') sobre IA generativa para participación: sin despliegue con ciudadanos ni proceso propio . Estudio sin despliegue.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -3049,17 +3045,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>De ciudadano a senador: la inteligencia artificial y la reinvención de la elaboración legislativa en Brasil”</t>
+          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Iniciativa del Senado Federal de Brasil que busca potenciar la participación ciudadana en el proceso legislativo mediante el uso de inteligencia artificial. El propósito principal es transformar a los ciudadanos de votantes ocasionales en participantes activos en la creación de leyes, utilizando herramientas digitales y IA para facilitar y enriquecer su involucramiento en el proceso legislativo.</t>
+          <t>Investigación académica (Co:Lab USP / Cátedra Brasil-Alemania, getip) sobre el uso de IA generativa para apoyar a la ciudadanía a redactar y estructurar propuestas en procesos de participación, tomando como referencia el orçamento participativo de São Paulo. Descrito como 'pesquisas em andamento' / proyecto de investigación-prototipo, no como una herramienta oficial desplegada en el proceso real (que opera vía la plataforma Participe+/Participe Mais de la Prefeitura, sin IA generativa confirmada).</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://rebootdemocracy.ai/blog/ai-lawmaking-brazil-senate</t>
+          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -3069,7 +3065,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Propuesta, pero no hay datos sobre que se vaya a ejecutar.</t>
+          <t>Investigación académica en curso ('pesquisas em andamento') sobre IA generativa para participación: sin despliegue con ciudadanos ni proceso propio . Estudio sin despliegue.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -3077,17 +3073,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Fala.BR</t>
+          <t>De ciudadano a senador: la inteligencia artificial y la reinvención de la elaboración legislativa en Brasil”</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Plataforma para solicitudes de acceso a información y manifestaciones de ouvidoria u "oficina de atención ciudadana" (reclamos, denuncias, sugerencias).</t>
+          <t>Iniciativa del Senado Federal de Brasil que busca potenciar la participación ciudadana en el proceso legislativo mediante el uso de inteligencia artificial. El propósito principal es transformar a los ciudadanos de votantes ocasionales en participantes activos en la creación de leyes, utilizando herramientas digitales y IA para facilitar y enriquecer su involucramiento en el proceso legislativo.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://falabr.cgu.gov.br/</t>
+          <t>https://rebootdemocracy.ai/blog/ai-lawmaking-brazil-senate</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -3097,7 +3093,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>Propuesta, pero no hay datos sobre que se vaya a ejecutar.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -3105,17 +3101,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Jaque</t>
+          <t>Fala.BR</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Secretario virtual basado en IA que guía a los ciudadanos a través de la Guía de Servicios digital del estado (portal unificado de trámites). Extrae información vía API de un catálogo centralizado y responde consultas ciudadanas sobre requisitos, horarios, ubicaciones y pasos para acceder a servicios públicos​oecd.org​oecd.org. Objetivo: mejorar la experiencia ciudadana en trámites, ofreciendo atención 24/7 y estandarizada.</t>
+          <t>Plataforma para solicitudes de acceso a información y manifestaciones de ouvidoria u "oficina de atención ciudadana" (reclamos, denuncias, sugerencias).</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://falabr.cgu.gov.br/</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -3133,17 +3129,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Mudamos</t>
+          <t>Jaque</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Es una plataforma digital desarrollada por el Instituto de Tecnología y Sociedad de Río (its Rio) para facilitar la creación y firma de proyectos de ley de iniciativa popular mediante el uso de tecnología blockchain, que garantiza la seguridad y verificabilidad de las firmas digitales.</t>
+          <t>Secretario virtual basado en IA que guía a los ciudadanos a través de la Guía de Servicios digital del estado (portal unificado de trámites). Extrae información vía API de un catálogo centralizado y responde consultas ciudadanas sobre requisitos, horarios, ubicaciones y pasos para acceder a servicios públicos​oecd.org​oecd.org. Objetivo: mejorar la experiencia ciudadana en trámites, ofreciendo atención 24/7 y estandarizada.</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://www.mudamos.org/</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -3153,7 +3149,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -3161,17 +3157,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>ParticipACT Brasil</t>
+          <t>Mudamos</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ParticipAct es una plataforma brasileña de ciencia ciudadana de código abierto que permite a los ciudadanos reportar problemas urbanos directamente a las agencias públicas a través de una aplicación web y móvil. Utiliza inteligencia artificial para facilitar el registro de los reportes, analizar los datos y mejorar la comunicación con el público mediante chatbots, con el fin de fomentar la colaboración para resolver los problemas de la ciudad.</t>
+          <t>Es una plataforma digital desarrollada por el Instituto de Tecnología y Sociedad de Río (its Rio) para facilitar la creación y firma de proyectos de ley de iniciativa popular mediante el uso de tecnología blockchain, que garantiza la seguridad y verificabilidad de las firmas digitales.</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://site.participact.com.br/</t>
+          <t>https://www.mudamos.org/</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -3181,7 +3177,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Civic tech de reporte urbano (app para reportar problemas): no es un proceso participativo.</t>
+          <t>No se identifica uso de IA.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -3189,17 +3185,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Participa+ Brasil</t>
+          <t>ParticipACT Brasil</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Participa + Brasil es una plataforma oficial del Gobierno Federal de Brasil que centraliza oportunidades de participación social, como consultas públicas, audiencias y consejos, permitiendo a los ciudadanos contribuir en la formulación de políticas públicas.</t>
+          <t>ParticipAct es una plataforma brasileña de ciencia ciudadana de código abierto que permite a los ciudadanos reportar problemas urbanos directamente a las agencias públicas a través de una aplicación web y móvil. Utiliza inteligencia artificial para facilitar el registro de los reportes, analizar los datos y mejorar la comunicación con el público mediante chatbots, con el fin de fomentar la colaboración para resolver los problemas de la ciudad.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://www.gov.br/participamaisbrasil/pagina-inicial</t>
+          <t>https://site.participact.com.br/</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -3209,7 +3205,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA.</t>
+          <t>Civic tech de reporte urbano (app para reportar problemas): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -3217,17 +3213,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Participe+ (ParticipeMais) - app estudiantil UnB-MDS de IA sobre contenidos de Brasil Participativo</t>
+          <t>Participa+ Brasil</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>El artefacto no opera un proceso participativo propio: es una aplicación cliente que recolecta (web scraping) los contenidos públicos de la plataforma federal Brasil Participativo (propuestas, planes y conferencias) y los presenta de forma mas accesible. Los procesos participativos subyacentes son los de Brasil Participativo (Secretaria-Geral da Presidencia / Secretaria Nacional de Participacao Social), que ya estan cubiertos por la ficha br-brasil-participativo-clustering-semantic. Participe+ es un proyecto de la disciplina mds (Metodos de Desenvolvimento de Software) de Ingenieria de Software de la Universidade de Brasilia (organizacion GitHub unb-mds), semestre 2025.1, con release v1.0.0 (09/07/2025). No es la plataforma oficial ni el pipeline oficial de IA de lappis/brisa; es un desarrollo estudiantil independiente construido sobre los datos de Brasil Participativo.</t>
+          <t>Participa + Brasil es una plataforma oficial del Gobierno Federal de Brasil que centraliza oportunidades de participación social, como consultas públicas, audiencias y consejos, permitiendo a los ciudadanos contribuir en la formulación de políticas públicas.</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/unb-mds/ParticipeMais</t>
+          <t>https://www.gov.br/participamaisbrasil/pagina-inicial</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -3237,7 +3233,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Aunque tecnicamente la IA si procesa el contenido de los aportes (agrupa por temas via hdbscan y clasifica en eixos por similitud semantica, ademas de resumir con LLM), el candidato incumple una condicion necesaria del criterio de inclusion ('si solo si caso distinto, desplegado oficialmente'): no hay despliegue oficial ni adopcion por la Secretaria Nacional de Participacao Social; es un ejercicio de la disciplina mds (Ingenieria de Software, UnB, org unb-mds, semestre 2025.1) con release v1.0.0 del 09/07/2025 y unico 'deploy' un sitio de documentacion en GitHub Pages, patron tipico de proyecto academico de un semestre, sin usuarios reales ni operacion gubernamental. substancial solapamiento con el caso ya contado br-brasil-participativo-clustering-semantic: opera sobre la misma plataforma Brasil Participativo (raspa sus propuestas), pertenece al mismo ecosistema UnB y replica la misma idea de clustering/clasificacion tematica de propuestas, pero como artefacto estudiantil paralelo, no como el pipeline oficial de lappis/brisa. Se distingue del municipal 'Participe+' de la Prefeitura de Sao Paulo (participemais.prefeitura.sp.gov.br), que es otro caso no relacionado. Por incumplir 'desplegado oficialmente' (ejercicio estudiantil sin adopcion) y por solapar con el caso federal ya contado, la decision es no. La duda central (¿va mas alla de resumir?) se resuelve a favor de 'si procesa contenido', pero eso no basta para entrar sin despliegue oficial.</t>
+          <t>No se identifica uso de IA.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -3245,17 +3241,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Projeto Lumina - análise de sentimentos das propostas de Brasil Participativo (projeto estudantil UnB-MDS)</t>
+          <t>Participe+ (ParticipeMais) - app estudiantil UnB-MDS de IA sobre contenidos de Brasil Participativo</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>El proceso participativo real subyacente es Brasil Participativo, la plataforma digital de participación social del Gobierno Federal de Brasil (construida sobre Decidim, lanzada en 2023 por la Secretaria-Geral da Presidência da República), donde la ciudadanía envía propuestas de texto libre, comentarios y votos sobre políticas públicas (PPA Participativo, Plano Clima, etc.). Projeto Lumina no es ese proceso ni un componente oficial de él: es un proyecto de software desarrollado por estudiantes en la disciplina 'Métodos de Desenvolvimento de Software' (mds) del curso de Engenharia de Software de la Universidade de Brasília (UnB-fga), semestre 2024-2, que aplica análisis de sentimiento (positivo/negativo/neutro) sobre las propuestas/comentarios de los Planos Participativos publicados en Brasil Participativo. Es un ejercicio académico (una webapp con documentación MkDocs y 'Versão Final' de fin de curso en feb-2025), no un despliegue oficial.</t>
+          <t>El artefacto no opera un proceso participativo propio: es una aplicación cliente que recolecta (web scraping) los contenidos públicos de la plataforma federal Brasil Participativo (propuestas, planes y conferencias) y los presenta de forma mas accesible. Los procesos participativos subyacentes son los de Brasil Participativo (Secretaria-Geral da Presidencia / Secretaria Nacional de Participacao Social), que ya estan cubiertos por la ficha br-brasil-participativo-clustering-semantic. Participe+ es un proyecto de la disciplina mds (Metodos de Desenvolvimento de Software) de Ingenieria de Software de la Universidade de Brasilia (organizacion GitHub unb-mds), semestre 2025.1, con release v1.0.0 (09/07/2025). No es la plataforma oficial ni el pipeline oficial de IA de lappis/brisa; es un desarrollo estudiantil independiente construido sobre los datos de Brasil Participativo.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/unb-mds/2024-2-Lumina</t>
+          <t>https://github.com/unb-mds/ParticipeMais</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -3265,7 +3261,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Aunque la IA sí actúa sobre el contenido de aportes ciudadanos (análisis de sentimiento positivo/negativo/neutro de las propuestas y comentarios de Brasil Participativo,, falla el requisito de despliegue oficial: Projeto Lumina es un ejercicio académico de la disciplina 'Métodos de Desenvolvimento de Software' del curso de Engenharia de Software de la UnB (semestre 2024-2), no un sistema adoptado ni operado por el gobierno. La señal del candidato conflaciona 'mds' (el nombre de la disciplina y de la org GitHub 'unb-mds') con 'Ministério do Desenvolvimento Social': no se halló evidencia de asociación oficial con ese Ministerio ni con la Secretaria Nacional de Participação Social, ni de integración en producción. El repositorio sigue el patrón idéntico de decenas de proyectos estudiantiles de 'unb-mds' (DFemObras, SuaGradeUnB, LicitaBSB, forUnB, GovInsights, etc.), tiene 3 stars/4 forks y su 'Versão Final' (feb-2025) marca el fin del curso. Sobre el doble conteo: no es un componente ni duplicado técnico de la ficha ya contada 'Brasil Participativo - clustering semántico' (esa es el pipeline oficial BERTopic+LLM de lappis/brisa con mentoría de la Secretaria de Participação Social); Lumina es un artefacto distinto (webapp estudiantil que consume datos de bp), pero igualmente inelegible por ser académico sin adopción. Conclusión: no por ejercicio académico sin despliegue oficial.</t>
+          <t>Aunque tecnicamente la IA si procesa el contenido de los aportes (agrupa por temas via hdbscan y clasifica en eixos por similitud semantica, ademas de resumir con LLM), el candidato incumple una condicion necesaria del criterio de inclusion ('si solo si caso distinto, desplegado oficialmente'): no hay despliegue oficial ni adopcion por la Secretaria Nacional de Participacao Social; es un ejercicio de la disciplina mds (Ingenieria de Software, UnB, org unb-mds, semestre 2025.1) con release v1.0.0 del 09/07/2025 y unico 'deploy' un sitio de documentacion en GitHub Pages, patron tipico de proyecto academico de un semestre, sin usuarios reales ni operacion gubernamental. substancial solapamiento con el caso ya contado br-brasil-participativo-clustering-semantic: opera sobre la misma plataforma Brasil Participativo (raspa sus propuestas), pertenece al mismo ecosistema UnB y replica la misma idea de clustering/clasificacion tematica de propuestas, pero como artefacto estudiantil paralelo, no como el pipeline oficial de lappis/brisa. Se distingue del municipal 'Participe+' de la Prefeitura de Sao Paulo (participemais.prefeitura.sp.gov.br), que es otro caso no relacionado. Por incumplir 'desplegado oficialmente' (ejercicio estudiantil sin adopcion) y por solapar con el caso federal ya contado, la decision es no. La duda central (¿va mas alla de resumir?) se resuelve a favor de 'si procesa contenido', pero eso no basta para entrar sin despliegue oficial.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -3273,17 +3269,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Querido Diário</t>
+          <t>Projeto Lumina - análise de sentimentos das propostas de Brasil Participativo (projeto estudantil UnB-MDS)</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Querido Diário es una plataforma de Open Knowledge Brasil que emplea inteligencia artificial para clasificar, contextualizar y expandir la información de los diarios oficiales municipales, haciéndolos accesibles en formato abierto y amigable. Al centralizar más de 850.000 diarios de 522 municipios, facilita el monitoreo ciudadano de actos oficiales y promueve el control social mediante búsquedas semánticas y una API abierta que integra estos datos en otras herramientas cívicas.</t>
+          <t>El proceso participativo real subyacente es Brasil Participativo, la plataforma digital de participación social del Gobierno Federal de Brasil (construida sobre Decidim, lanzada en 2023 por la Secretaria-Geral da Presidência da República), donde la ciudadanía envía propuestas de texto libre, comentarios y votos sobre políticas públicas (PPA Participativo, Plano Clima, etc.). Projeto Lumina no es ese proceso ni un componente oficial de él: es un proyecto de software desarrollado por estudiantes en la disciplina 'Métodos de Desenvolvimento de Software' (mds) del curso de Engenharia de Software de la Universidade de Brasília (UnB-fga), semestre 2024-2, que aplica análisis de sentimiento (positivo/negativo/neutro) sobre las propuestas/comentarios de los Planos Participativos publicados en Brasil Participativo. Es un ejercicio académico (una webapp con documentación MkDocs y 'Versão Final' de fin de curso en feb-2025), no un despliegue oficial.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://ok.org.br/projetos/querido-diario/</t>
+          <t>https://github.com/unb-mds/2024-2-Lumina</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -3293,7 +3289,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Aunque la IA sí actúa sobre el contenido de aportes ciudadanos (análisis de sentimiento positivo/negativo/neutro de las propuestas y comentarios de Brasil Participativo,, falla el requisito de despliegue oficial: Projeto Lumina es un ejercicio académico de la disciplina 'Métodos de Desenvolvimento de Software' del curso de Engenharia de Software de la UnB (semestre 2024-2), no un sistema adoptado ni operado por el gobierno. La señal del candidato conflaciona 'mds' (el nombre de la disciplina y de la org GitHub 'unb-mds') con 'Ministério do Desenvolvimento Social': no se halló evidencia de asociación oficial con ese Ministerio ni con la Secretaria Nacional de Participação Social, ni de integración en producción. El repositorio sigue el patrón idéntico de decenas de proyectos estudiantiles de 'unb-mds' (DFemObras, SuaGradeUnB, LicitaBSB, forUnB, GovInsights, etc.), tiene 3 stars/4 forks y su 'Versão Final' (feb-2025) marca el fin del curso. Sobre el doble conteo: no es un componente ni duplicado técnico de la ficha ya contada 'Brasil Participativo - clustering semántico' (esa es el pipeline oficial BERTopic+LLM de lappis/brisa con mentoría de la Secretaria de Participação Social); Lumina es un artefacto distinto (webapp estudiantil que consume datos de bp), pero igualmente inelegible por ser académico sin adopción. Conclusión: no por ejercicio académico sin despliegue oficial.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
@@ -3301,17 +3297,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Robô ALICE (CGU)</t>
+          <t>Querido Diário</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Robô alice es una herramienta de inteligencia artificial desarrollada por la CGU para automatizar el análisis de datos en procesos de compras públicas, permitiendo identificar patrones y posibles irregularidades en la administración pública.</t>
+          <t>Querido Diário es una plataforma de Open Knowledge Brasil que emplea inteligencia artificial para clasificar, contextualizar y expandir la información de los diarios oficiales municipales, haciéndolos accesibles en formato abierto y amigable. Al centralizar más de 850.000 diarios de 522 municipios, facilita el monitoreo ciudadano de actos oficiales y promueve el control social mediante búsquedas semánticas y una API abierta que integra estos datos en otras herramientas cívicas.</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>https://oecd-opsi.org/innovations/robot-alice-bid-contract-and-notice-analyser/</t>
+          <t>https://ok.org.br/projetos/querido-diario/</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -3329,17 +3325,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Serenata.ai</t>
+          <t>Robô ALICE (CGU)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Serenata.ai es el sitio web oficial de la Operación Serenata de Amor, un proyecto brasileño de innovación cívica. Su objetivo principal es fiscalizar el uso de fondos públicos por parte de diputados y senadores, utilizando técnicas de IA para detectar posibles irregularidades en los reembolsos solicitados por los parlamentarios.</t>
+          <t>Robô alice es una herramienta de inteligencia artificial desarrollada por la CGU para automatizar el análisis de datos en procesos de compras públicas, permitiendo identificar patrones y posibles irregularidades en la administración pública.</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://serenata.ai/</t>
+          <t>https://oecd-opsi.org/innovations/robot-alice-bid-contract-and-notice-analyser/</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -3349,7 +3345,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>No es participación Ciudadana.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
@@ -3357,33 +3353,61 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>Serenata.ai</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Serenata.ai es el sitio web oficial de la Operación Serenata de Amor, un proyecto brasileño de innovación cívica. Su objetivo principal es fiscalizar el uso de fondos públicos por parte de diputados y senadores, utilizando técnicas de IA para detectar posibles irregularidades en los reembolsos solicitados por los parlamentarios.</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>https://serenata.ai/</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>No es participación Ciudadana.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>Tira-Dúvidas TSE</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Chatbot WhatsApp con verificador automático de desinformación y búsqueda semántica de normas.</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>https://www.tse.jus.br/comunicacao/noticias/2022/Setembro/tira-duvidas-do-tse-no-whatsapp-ganha-ferramenta-inedita-de-checagem-de-fatos-para-as-eleicoes-2022-402542</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Atencion ciudadana.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F24"/>
+  <autoFilter ref="A1:F25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
